--- a/stories/arbres/TREE-COL-033.xlsx
+++ b/stories/arbres/TREE-COL-033.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Kenzo est avec maman, au parc. Kenzo a envie de jouer. maman est là, tout près. On va apprendre : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo écoute maman. Kenzo entend les mots : écouter, si malaise raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Kenzo va vers le bac à sable. La couverture est douce. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Kenzo se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On se tient la main. maman dit : je suis là. On reste ensemble.</t>
+          <t>Kenzo va vers le bac à sable. La couverture est douce. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Kenzo se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On se tient la main. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo va vers le bac à sable. La couverture est douce. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Kenzo se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On se tient la main.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1862,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2035,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo respire. Kenzo retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2226,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2393,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le ballon. Ça sent le pain chaud. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On souffle doucement. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2533,6 +2586,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2697,6 +2755,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Tom. Une feuille tombe. On se tient la main. Cette fin-là est celle de le bac à sable, le ballon et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2922,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3089,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Léa. L'eau coule, tout petit bruit. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3256,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3423,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Sami. Un vélo passe au loin. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3590,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3669,6 +3757,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le seau. Le vent est doux. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3857,6 +3950,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4021,6 +4119,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Tom. L'eau coule, tout petit bruit. On se tient la main. Cette fin-là est celle de le bac à sable, le seau et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4183,6 +4286,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4345,6 +4453,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Léa. Un vélo passe au loin. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4507,6 +4620,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4669,6 +4787,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Sami. La lumière est claire. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4831,6 +4954,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4993,6 +5121,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le doudou. Le sol est un peu froid. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5181,6 +5314,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5345,6 +5483,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Tom. Un vélo passe au loin. On se tient la main. Cette fin-là est celle de le bac à sable, le doudou et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5507,6 +5650,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5669,6 +5817,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Léa. La lumière est claire. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5831,6 +5984,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5993,6 +6151,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Sami. Il y a des miettes sur la table. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6155,6 +6318,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6179,7 +6347,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Kenzo va vers le toboggan. On entend un oiseau. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Kenzo se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On range un objet. maman dit : je suis là. On reste ensemble.</t>
+          <t>Kenzo va vers le toboggan. On entend un oiseau. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Kenzo se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On range un objet. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6317,6 +6485,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo va vers le toboggan. On entend un oiseau. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Kenzo se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On range un objet.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6497,6 +6671,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
     </row>
@@ -6665,6 +6844,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo respire. Kenzo retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6851,6 +7035,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7013,6 +7202,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le ballon. Une feuille tombe. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On souffle doucement. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7201,6 +7395,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7365,6 +7564,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Tom. L'eau coule, tout petit bruit. On range un objet. Cette fin-là est celle de le toboggan, le ballon et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7527,6 +7731,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7689,6 +7898,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Léa. Un vélo passe au loin. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7851,6 +8065,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8013,6 +8232,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Sami. La lumière est claire. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8175,6 +8399,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8337,6 +8566,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le seau. L'eau coule, tout petit bruit. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8525,6 +8759,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8689,6 +8928,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Tom. Un vélo passe au loin. On range un objet. Cette fin-là est celle de le toboggan, le seau et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8851,6 +9095,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9013,6 +9262,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Léa. La lumière est claire. On dit merci. Cette fin-là est celle de le toboggan, le seau et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9175,6 +9429,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9337,6 +9596,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Sami. Il y a des miettes sur la table. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9499,6 +9763,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9661,6 +9930,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le doudou. Un vélo passe au loin. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9849,6 +10123,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10013,6 +10292,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Tom. La lumière est claire. On range un objet. Cette fin-là est celle de le toboggan, le doudou et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10175,6 +10459,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10337,6 +10626,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Léa. Il y a des miettes sur la table. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10499,6 +10793,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10661,6 +10960,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Sami. Un chat miaule une fois. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10823,6 +11127,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10847,7 +11156,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Kenzo va vers les balançoires. Ça sent le pain chaud. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Kenzo se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On dit merci. maman dit : je suis là. On reste ensemble.</t>
+          <t>Kenzo va vers les balançoires. Ça sent le pain chaud. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Kenzo se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On dit merci. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10985,6 +11294,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo va vers les balançoires. Ça sent le pain chaud. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Kenzo se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On dit merci.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11165,6 +11480,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
     </row>
@@ -11333,6 +11653,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo respire. Kenzo retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11519,6 +11844,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11681,6 +12011,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le ballon. La lumière est claire. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On souffle doucement. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11869,6 +12204,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12033,6 +12373,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Tom. Un vélo passe au loin. On dit merci. Cette fin-là est celle de les balançoires, le ballon et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12195,6 +12540,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12357,6 +12707,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Léa. La lumière est claire. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12519,6 +12874,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12681,6 +13041,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Sami. Il y a des miettes sur la table. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12843,6 +13208,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13005,6 +13375,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le seau. Il y a des miettes sur la table. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13193,6 +13568,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13357,6 +13737,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Tom. La lumière est claire. On dit merci. Cette fin-là est celle de les balançoires, le seau et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13519,6 +13904,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13681,6 +14071,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Léa. Il y a des miettes sur la table. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13843,6 +14238,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14005,6 +14405,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Sami. Un chat miaule une fois. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14167,6 +14572,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14329,6 +14739,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le doudou. Un chat miaule une fois. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14517,6 +14932,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14681,6 +15101,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Tom. Il y a des miettes sur la table. On dit merci. Cette fin-là est celle de les balançoires, le doudou et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14843,6 +15268,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15005,6 +15435,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Léa. Un chat miaule une fois. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15167,6 +15602,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15329,6 +15769,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Sami. Les chaussures font toc toc. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15491,6 +15936,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15509,7 +15959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15582,6 +16032,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-033.xlsx
+++ b/stories/arbres/TREE-COL-033.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,11 @@
           <t>narrateur|Aujourd'hui, Kenzo est avec maman, au parc. Kenzo a envie de jouer. maman est là, tout près. On va apprendre : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo écoute maman. Kenzo entend les mots : écouter, si malaise raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1524,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1693,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1869,6 +1881,7 @@
           <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2040,6 +2053,7 @@
           <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo respire. Kenzo retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2231,6 +2245,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2398,6 +2413,7 @@
           <t>narrateur|Kenzo a choisi le ballon. Ça sent le pain chaud. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On souffle doucement. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2593,6 +2609,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2760,6 +2777,7 @@
           <t>narrateur|Kenzo rejoint Tom. Une feuille tombe. On se tient la main. Cette fin-là est celle de le bac à sable, le ballon et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2927,6 +2945,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3094,6 +3113,7 @@
           <t>narrateur|Kenzo rejoint Léa. L'eau coule, tout petit bruit. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3261,6 +3281,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3428,6 +3449,7 @@
           <t>narrateur|Kenzo rejoint Sami. Un vélo passe au loin. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3595,6 +3617,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3762,6 +3785,7 @@
           <t>narrateur|Kenzo a choisi le seau. Le vent est doux. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3957,6 +3981,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4124,6 +4149,7 @@
           <t>narrateur|Kenzo rejoint Tom. L'eau coule, tout petit bruit. On se tient la main. Cette fin-là est celle de le bac à sable, le seau et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4291,6 +4317,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4458,6 +4485,7 @@
           <t>narrateur|Kenzo rejoint Léa. Un vélo passe au loin. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4625,6 +4653,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4792,6 +4821,7 @@
           <t>narrateur|Kenzo rejoint Sami. La lumière est claire. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4959,6 +4989,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5126,6 +5157,7 @@
           <t>narrateur|Kenzo a choisi le doudou. Le sol est un peu froid. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5321,6 +5353,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5488,6 +5521,7 @@
           <t>narrateur|Kenzo rejoint Tom. Un vélo passe au loin. On se tient la main. Cette fin-là est celle de le bac à sable, le doudou et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5655,6 +5689,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5822,6 +5857,7 @@
           <t>narrateur|Kenzo rejoint Léa. La lumière est claire. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5989,6 +6025,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6156,6 +6193,7 @@
           <t>narrateur|Kenzo rejoint Sami. Il y a des miettes sur la table. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6323,6 +6361,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6491,6 +6530,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6678,6 +6718,7 @@
           <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6849,6 +6890,7 @@
           <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo respire. Kenzo retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7040,6 +7082,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7207,6 +7250,7 @@
           <t>narrateur|Kenzo a choisi le ballon. Une feuille tombe. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On souffle doucement. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7402,6 +7446,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7569,6 +7614,7 @@
           <t>narrateur|Kenzo rejoint Tom. L'eau coule, tout petit bruit. On range un objet. Cette fin-là est celle de le toboggan, le ballon et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7736,6 +7782,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7903,6 +7950,7 @@
           <t>narrateur|Kenzo rejoint Léa. Un vélo passe au loin. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8070,6 +8118,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8237,6 +8286,7 @@
           <t>narrateur|Kenzo rejoint Sami. La lumière est claire. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8404,6 +8454,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8571,6 +8622,7 @@
           <t>narrateur|Kenzo a choisi le seau. L'eau coule, tout petit bruit. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8766,6 +8818,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8933,6 +8986,7 @@
           <t>narrateur|Kenzo rejoint Tom. Un vélo passe au loin. On range un objet. Cette fin-là est celle de le toboggan, le seau et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9100,6 +9154,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9267,6 +9322,7 @@
           <t>narrateur|Kenzo rejoint Léa. La lumière est claire. On dit merci. Cette fin-là est celle de le toboggan, le seau et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9434,6 +9490,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9601,6 +9658,7 @@
           <t>narrateur|Kenzo rejoint Sami. Il y a des miettes sur la table. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9768,6 +9826,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9935,6 +9994,7 @@
           <t>narrateur|Kenzo a choisi le doudou. Un vélo passe au loin. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10130,6 +10190,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10297,6 +10358,7 @@
           <t>narrateur|Kenzo rejoint Tom. La lumière est claire. On range un objet. Cette fin-là est celle de le toboggan, le doudou et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10464,6 +10526,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10631,6 +10694,7 @@
           <t>narrateur|Kenzo rejoint Léa. Il y a des miettes sur la table. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10798,6 +10862,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10965,6 +11030,7 @@
           <t>narrateur|Kenzo rejoint Sami. Un chat miaule une fois. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11132,6 +11198,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11300,6 +11367,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11487,6 +11555,7 @@
           <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11658,6 +11727,7 @@
           <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo respire. Kenzo retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11849,6 +11919,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12016,6 +12087,7 @@
           <t>narrateur|Kenzo a choisi le ballon. La lumière est claire. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On souffle doucement. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12211,6 +12283,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12378,6 +12451,7 @@
           <t>narrateur|Kenzo rejoint Tom. Un vélo passe au loin. On dit merci. Cette fin-là est celle de les balançoires, le ballon et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12545,6 +12619,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12712,6 +12787,7 @@
           <t>narrateur|Kenzo rejoint Léa. La lumière est claire. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12879,6 +12955,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13046,6 +13123,7 @@
           <t>narrateur|Kenzo rejoint Sami. Il y a des miettes sur la table. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13213,6 +13291,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13380,6 +13459,7 @@
           <t>narrateur|Kenzo a choisi le seau. Il y a des miettes sur la table. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13575,6 +13655,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13742,6 +13823,7 @@
           <t>narrateur|Kenzo rejoint Tom. La lumière est claire. On dit merci. Cette fin-là est celle de les balançoires, le seau et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13909,6 +13991,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14076,6 +14159,7 @@
           <t>narrateur|Kenzo rejoint Léa. Il y a des miettes sur la table. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14243,6 +14327,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14410,6 +14495,7 @@
           <t>narrateur|Kenzo rejoint Sami. Un chat miaule une fois. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14577,6 +14663,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14744,6 +14831,7 @@
           <t>narrateur|Kenzo a choisi le doudou. Un chat miaule une fois. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14939,6 +15027,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15106,6 +15195,7 @@
           <t>narrateur|Kenzo rejoint Tom. Il y a des miettes sur la table. On dit merci. Cette fin-là est celle de les balançoires, le doudou et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15273,6 +15363,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15440,6 +15531,7 @@
           <t>narrateur|Kenzo rejoint Léa. Un chat miaule une fois. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15607,6 +15699,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15774,6 +15867,7 @@
           <t>narrateur|Kenzo rejoint Sami. Les chaussures font toc toc. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15941,6 +16035,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15959,7 +16054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16039,6 +16134,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16053,7 +16162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16240,6 +16349,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-COL-033.xlsx
+++ b/stories/arbres/TREE-COL-033.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Écouter la maîtresse, en parler à la maison — au parc</t>
+          <t>La chaîne tiède et le galet</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La chaîne de la balançoire est tiède. Un galet reste dans la poche. Nino a écouté la maîtresse. Si le ventre se serre, il raconte à papa ou maman.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Kenzo est avec maman, au parc. Kenzo a envie de jouer. maman est là, tout près. On va apprendre : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo écoute maman. Kenzo entend les mots : écouter, si malaise raconter à la maison.</t>
+          <t>La chaîne de la balançoire est tiède. Elle fait tic, tout petit, contre le poteau. Un manteau jaune est plié sur le banc. Une flaque tient le ciel, tout bas. Ça sent l'herbe coupée, encore. Un pigeon picore une miette, tout près. Le cartable de Nino s'appuie contre le banc. Il sent encore la craie de l'école. Un galet froid reste dans la poche. Nino, tu as encore tes chaussures d'école. Elles sont un peu poussiéreuses. Le parc est calme, ce soir-là. En ce moment, Nino pose la main sur la chaîne. Le métal est tiède, un peu rugueux. La maîtresse a parlé, ce matin. Nino écoute encore, dans sa tête. J'ai écouté, maman. Oui. On écoute la maîtresse. Et si le ventre se serre ? On raconte à papa ou maman, à la maison. Au parc aussi, on raconte. Le bac à sable attend, tout blond. Le toboggan tient encore le soleil. Les balançoires bougent, tout doux. Papa, on va là-bas ? On y va. On t'écoute, Nino.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,12 +1337,39 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aujourd'hui, Kenzo est avec maman, au parc. Kenzo a envie de jouer. maman est là, tout près. On va apprendre : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo écoute maman. Kenzo entend les mots : écouter, si malaise raconter à la maison.</t>
+          <t>narrateur|La chaîne de la balançoire est tiède.
+narrateur|Elle fait tic, tout petit, contre le poteau.
+narrateur|Un manteau jaune est plié sur le banc.
+narrateur|Une flaque tient le ciel, tout bas.
+narrateur|Ça sent l'herbe coupée, encore.
+narrateur|Un pigeon picore une miette, tout près.
+narrateur|Le cartable de Nino s'appuie contre le banc.
+narrateur|Il sent encore la craie de l'école.
+narrateur|Un galet froid reste dans la poche.
+maman|Nino, tu as encore tes chaussures d'école.
+maman|Elles sont un peu poussiéreuses.
+papa|Le parc est calme, ce soir-là.
+narrateur|En ce moment, Nino pose la main sur la chaîne.
+narrateur|Le métal est tiède, un peu rugueux.
+narrateur|La maîtresse a parlé, ce matin.
+narrateur|Nino écoute encore, dans sa tête.
+enfant-m|J'ai écouté, maman.
+maman|Oui.
+maman|On écoute la maîtresse.
+papa|Et si le ventre se serre ?
+maman|On raconte à papa ou maman, à la maison.
+papa|Au parc aussi, on raconte.
+narrateur|Le bac à sable attend, tout blond.
+narrateur|Le toboggan tient encore le soleil.
+narrateur|Les balançoires bougent, tout doux.
+enfant-m|Papa, on va là-bas ?
+papa|On y va.
+maman|On t'écoute, Nino.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>enfants_parc,chaine</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1396,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>Où va Nino, dans le parc ? Le bac à sable, le toboggan, ou les balançoires ? On écoute. Et on raconte, si malaise.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1521,7 +1560,10 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>narrateur|Où va Nino, dans le parc ?
+papa|Le bac à sable, le toboggan, ou les balançoires ?
+maman|On écoute.
+maman|Et on raconte, si malaise.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1549,7 +1591,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Kenzo va vers le bac à sable. La couverture est douce. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Kenzo se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On se tient la main. Je suis là. On reste ensemble.</t>
+          <t>Nino s'assoit au bord du bac. Le sable est frais, un peu blond. Le bois du rebord est lisse, tout gris. Une petite pelle rouge attend dedans. L'ombre du manteau jaune tombe ici. Le sable est doux, Nino. Tu veux la pelle ? Oui, maman. Nino prend le manche. Il est un peu rêche. Le galet reste froid, dans la poche. Un souvenir revient, tout près. Quelqu'un a parlé tout bas, à l'école. Le ventre de Nino se serre. Maman. J'ai eu un malaise. C'était un secret, tout bas. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, tu viens nous le dire. Je t'écoute, moi aussi. Bravo, Nino. Le sable coule entre les doigts. Le ventre se desserre, tout doux. Je raconte à la maison. Au parc aussi, on raconte.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1689,11 +1731,39 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo va vers le bac à sable. La couverture est douce. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Kenzo se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On se tient la main.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nino s'assoit au bord du bac.
+narrateur|Le sable est frais, un peu blond.
+narrateur|Le bois du rebord est lisse, tout gris.
+narrateur|Une petite pelle rouge attend dedans.
+narrateur|L'ombre du manteau jaune tombe ici.
+maman|Le sable est doux, Nino.
+maman|Tu veux la pelle ?
+enfant-m|Oui, maman.
+narrateur|Nino prend le manche.
+narrateur|Il est un peu rêche.
+narrateur|Le galet reste froid, dans la poche.
+narrateur|Un souvenir revient, tout près.
+narrateur|Quelqu'un a parlé tout bas, à l'école.
+narrateur|Le ventre de Nino se serre.
+enfant-m|Maman.
+enfant-m|J'ai eu un malaise.
+enfant-m|C'était un secret, tout bas.
+maman|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, tu viens nous le dire.
+papa|Je t'écoute, moi aussi.
+papa|Bravo, Nino.
+narrateur|Le sable coule entre les doigts.
+narrateur|Le ventre se desserre, tout doux.
+enfant-m|Je raconte à la maison.
+maman|Au parc aussi, on raconte.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>sable</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1718,7 +1788,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>Nino a un malaise, au bac. Que fait-il ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1878,7 +1948,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>narrateur|Nino a un malaise, au bac.
+maman|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1906,7 +1977,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo respire. Kenzo retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+          <t>Oui. On écoute la maîtresse. Si malaise, on raconte. Nino souffle un peu. Je raconte à papa et maman. Bravo, Nino. C'est du bon travail. La pelle rouge reste dans le sable.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2050,7 +2121,14 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo respire. Kenzo retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+          <t>maman|Oui.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte.
+narrateur|Nino souffle un peu.
+enfant-m|Je raconte à papa et maman.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La pelle rouge reste dans le sable.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2078,7 +2156,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Trois jouets attendent, dans l'herbe. Le ballon, le seau, ou le doudou ? On joue. On écoute. Et on raconte, si malaise.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2242,7 +2320,11 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|Trois jouets attendent, dans l'herbe.
+maman|Le ballon, le seau, ou le doudou ?
+papa|On joue.
+papa|On écoute.
+papa|Et on raconte, si malaise.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2270,7 +2352,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a choisi le ballon. Ça sent le pain chaud. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On souffle doucement. papa n'est pas loin.</t>
+          <t>Nino prend le ballon rouge. Il sent le caoutchouc, un peu chaud. Une miette colle encore dessus. Tu veux le lancer, tout doux ? Oui, papa. Papa parle d'abord, tout calme. Nino écoute jusqu'au bout. Le ballon est chaud. Tu as écouté. Bravo. Le ballon fait un petit poum, dans l'herbe. Le ballon laisse un rond, dans le sable. On est encore près de le bac à sable. On écoute. Si malaise, on raconte.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2410,10 +2492,28 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo a choisi le ballon. Ça sent le pain chaud. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On souffle doucement. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+          <t>narrateur|Nino prend le ballon rouge.
+narrateur|Il sent le caoutchouc, un peu chaud.
+narrateur|Une miette colle encore dessus.
+papa|Tu veux le lancer, tout doux ?
+enfant-m|Oui, papa.
+narrateur|Papa parle d'abord, tout calme.
+narrateur|Nino écoute jusqu'au bout.
+enfant-m|Le ballon est chaud.
+maman|Tu as écouté.
+maman|Bravo.
+narrateur|Le ballon fait un petit poum, dans l'herbe.
+narrateur|Le ballon laisse un rond, dans le sable.
+narrateur|On est encore près de le bac à sable.
+maman|On écoute.
+maman|Si malaise, on raconte.</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>ballon</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2438,7 +2538,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois coins du parc attendent. Le banc, la marelle, ou le cerceau ? On écoute d'abord. Puis on raconte.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2606,7 +2706,10 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois coins du parc attendent.
+papa|Le banc, la marelle, ou le cerceau ?
+maman|On écoute d'abord.
+maman|Puis on raconte.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2634,7 +2737,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint Tom. Une feuille tombe. On se tient la main. Cette fin-là est celle de le bac à sable, le ballon et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+          <t>Le banc de bois est encore tiède. Le manteau jaune y fait un tas. Une flaque tient le ciel, tout bas. Nino a encore le ballon. Il est près de le bac à sable. Le ballon s'appuie contre le banc. Tu as encore un mot, Nino ? Nino respire. J'ai écouté la maîtresse. Si malaise, je raconte. Bravo. Tu as écouté. Puis tu as raconté. C'est du bon travail, Nino. Merci, papa. Merci, maman. Le banc reste tout près.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2774,10 +2877,30 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint Tom. Une feuille tombe. On se tient la main. Cette fin-là est celle de le bac à sable, le ballon et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr"/>
+          <t>narrateur|Le banc de bois est encore tiède.
+narrateur|Le manteau jaune y fait un tas.
+narrateur|Une flaque tient le ciel, tout bas.
+narrateur|Nino a encore le ballon.
+narrateur|Il est près de le bac à sable.
+narrateur|Le ballon s'appuie contre le banc.
+papa|Tu as encore un mot, Nino ?
+narrateur|Nino respire.
+enfant-m|J'ai écouté la maîtresse.
+enfant-m|Si malaise, je raconte.
+maman|Bravo.
+maman|Tu as écouté.
+maman|Puis tu as raconté.
+papa|C'est du bon travail, Nino.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Le banc reste tout près.</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>banc</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2802,7 +2925,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Nino a choisi le bac à sable. Il avait le ballon. Il est allé vers le banc. Bravo, Nino. C'est du bon travail. Le manteau jaune reste plié, tout calme. La chaîne de la balançoire se tait. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2942,7 +3065,16 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Nino a choisi le bac à sable.
+narrateur|Il avait le ballon.
+narrateur|Il est allé vers le banc.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le manteau jaune reste plié, tout calme.
+narrateur|La chaîne de la balançoire se tait.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2970,7 +3102,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint Léa. L'eau coule, tout petit bruit. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+          <t>La marelle a des cases, à la craie. Une case est un peu effacée. La craie sent l'école, encore. Nino a encore le ballon. Il est près de le bac à sable. Le ballon roule sur une case, tout doux. Tu as encore un mot, Nino ? Nino respire. J'ai écouté la maîtresse. Si malaise, je raconte. Bravo. Tu as écouté. Puis tu as raconté. C'est du bon travail, Nino. Merci, papa. Merci, maman. La marelle reste tout près.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3110,10 +3242,30 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint Léa. L'eau coule, tout petit bruit. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr"/>
+          <t>narrateur|La marelle a des cases, à la craie.
+narrateur|Une case est un peu effacée.
+narrateur|La craie sent l'école, encore.
+narrateur|Nino a encore le ballon.
+narrateur|Il est près de le bac à sable.
+narrateur|Le ballon roule sur une case, tout doux.
+papa|Tu as encore un mot, Nino ?
+narrateur|Nino respire.
+enfant-m|J'ai écouté la maîtresse.
+enfant-m|Si malaise, je raconte.
+maman|Bravo.
+maman|Tu as écouté.
+maman|Puis tu as raconté.
+papa|C'est du bon travail, Nino.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|La marelle reste tout près.</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>craie</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3138,7 +3290,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Nino a choisi le bac à sable. Il avait le ballon. Il est allé vers la marelle. Bravo, Nino. C'est du bon travail. La craie de la marelle sèche, tout pâle. La chaîne de la balançoire se tait. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3278,7 +3430,16 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Nino a choisi le bac à sable.
+narrateur|Il avait le ballon.
+narrateur|Il est allé vers la marelle.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La craie de la marelle sèche, tout pâle.
+narrateur|La chaîne de la balançoire se tait.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3306,7 +3467,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint Sami. Un vélo passe au loin. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+          <t>Le cerceau jaune est dans l'herbe. Il est un peu chaud, au soleil. Une tige d'herbe passe au milieu. Nino a encore le ballon. Il est près de le bac à sable. Le ballon entre dans le cerceau, tout juste. Tu as encore un mot, Nino ? Nino respire. J'ai écouté la maîtresse. Si malaise, je raconte. Bravo. Tu as écouté. Puis tu as raconté. C'est du bon travail, Nino. Merci, papa. Merci, maman. Le cerceau reste tout près.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3446,10 +3607,30 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint Sami. Un vélo passe au loin. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr"/>
+          <t>narrateur|Le cerceau jaune est dans l'herbe.
+narrateur|Il est un peu chaud, au soleil.
+narrateur|Une tige d'herbe passe au milieu.
+narrateur|Nino a encore le ballon.
+narrateur|Il est près de le bac à sable.
+narrateur|Le ballon entre dans le cerceau, tout juste.
+papa|Tu as encore un mot, Nino ?
+narrateur|Nino respire.
+enfant-m|J'ai écouté la maîtresse.
+enfant-m|Si malaise, je raconte.
+maman|Bravo.
+maman|Tu as écouté.
+maman|Puis tu as raconté.
+papa|C'est du bon travail, Nino.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Le cerceau reste tout près.</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>cerceau</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3474,7 +3655,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Nino a choisi le bac à sable. Il avait le ballon. Il est allé vers le cerceau. Bravo, Nino. C'est du bon travail. Le cerceau jaune dort dans l'herbe. La chaîne de la balançoire se tait. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3614,7 +3795,16 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Nino a choisi le bac à sable.
+narrateur|Il avait le ballon.
+narrateur|Il est allé vers le cerceau.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le cerceau jaune dort dans l'herbe.
+narrateur|La chaîne de la balançoire se tait.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3642,7 +3832,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a choisi le seau. Le vent est doux. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
+          <t>Nino prend le seau bleu. Le plastique est un peu froid. Un peu de sable reste au fond. Tu veux remplir le seau ? Oui, maman. Maman parle d'abord. Nino écoute. Le seau est froid. Tu as écouté. Bravo, Nino. Le seau tapote le bois, tout fin. Le seau prend du sable blond, tout frais. On est encore près de le bac à sable. On écoute. Si malaise, on raconte.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3782,10 +3972,28 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo a choisi le seau. Le vent est doux. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr"/>
+          <t>narrateur|Nino prend le seau bleu.
+narrateur|Le plastique est un peu froid.
+narrateur|Un peu de sable reste au fond.
+maman|Tu veux remplir le seau ?
+enfant-m|Oui, maman.
+narrateur|Maman parle d'abord.
+narrateur|Nino écoute.
+enfant-m|Le seau est froid.
+papa|Tu as écouté.
+papa|Bravo, Nino.
+narrateur|Le seau tapote le bois, tout fin.
+narrateur|Le seau prend du sable blond, tout frais.
+narrateur|On est encore près de le bac à sable.
+maman|On écoute.
+maman|Si malaise, on raconte.</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>seau</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3810,7 +4018,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois coins du parc attendent. Le banc, la marelle, ou le cerceau ? On écoute d'abord. Puis on raconte.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3978,7 +4186,10 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois coins du parc attendent.
+papa|Le banc, la marelle, ou le cerceau ?
+maman|On écoute d'abord.
+maman|Puis on raconte.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -4006,7 +4217,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint Tom. L'eau coule, tout petit bruit. On se tient la main. Cette fin-là est celle de le bac à sable, le seau et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+          <t>Le banc de bois est encore tiède. Le manteau jaune y fait un tas. Une flaque tient le ciel, tout bas. Nino a encore le seau. Il est près de le bac à sable. Le seau bleu pose au pied du banc. Tu as encore un mot, Nino ? Nino respire. J'ai écouté la maîtresse. Si malaise, je raconte. Bravo. Tu as écouté. Puis tu as raconté. C'est du bon travail, Nino. Merci, papa. Merci, maman. Le banc reste tout près.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4146,10 +4357,30 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint Tom. L'eau coule, tout petit bruit. On se tient la main. Cette fin-là est celle de le bac à sable, le seau et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr"/>
+          <t>narrateur|Le banc de bois est encore tiède.
+narrateur|Le manteau jaune y fait un tas.
+narrateur|Une flaque tient le ciel, tout bas.
+narrateur|Nino a encore le seau.
+narrateur|Il est près de le bac à sable.
+narrateur|Le seau bleu pose au pied du banc.
+papa|Tu as encore un mot, Nino ?
+narrateur|Nino respire.
+enfant-m|J'ai écouté la maîtresse.
+enfant-m|Si malaise, je raconte.
+maman|Bravo.
+maman|Tu as écouté.
+maman|Puis tu as raconté.
+papa|C'est du bon travail, Nino.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Le banc reste tout près.</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>banc</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4174,7 +4405,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Nino a choisi le bac à sable. Il avait le seau. Il est allé vers le banc. Bravo, Nino. C'est du bon travail. Le manteau jaune reste plié, tout calme. La chaîne de la balançoire se tait. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4314,7 +4545,16 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Nino a choisi le bac à sable.
+narrateur|Il avait le seau.
+narrateur|Il est allé vers le banc.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le manteau jaune reste plié, tout calme.
+narrateur|La chaîne de la balançoire se tait.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4342,7 +4582,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint Léa. Un vélo passe au loin. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+          <t>La marelle a des cases, à la craie. Une case est un peu effacée. La craie sent l'école, encore. Nino a encore le seau. Il est près de le bac à sable. Un peu de sable tombe sur la marelle. Tu as encore un mot, Nino ? Nino respire. J'ai écouté la maîtresse. Si malaise, je raconte. Bravo. Tu as écouté. Puis tu as raconté. C'est du bon travail, Nino. Merci, papa. Merci, maman. La marelle reste tout près.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4482,10 +4722,30 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint Léa. Un vélo passe au loin. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr"/>
+          <t>narrateur|La marelle a des cases, à la craie.
+narrateur|Une case est un peu effacée.
+narrateur|La craie sent l'école, encore.
+narrateur|Nino a encore le seau.
+narrateur|Il est près de le bac à sable.
+narrateur|Un peu de sable tombe sur la marelle.
+papa|Tu as encore un mot, Nino ?
+narrateur|Nino respire.
+enfant-m|J'ai écouté la maîtresse.
+enfant-m|Si malaise, je raconte.
+maman|Bravo.
+maman|Tu as écouté.
+maman|Puis tu as raconté.
+papa|C'est du bon travail, Nino.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|La marelle reste tout près.</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>craie</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4510,7 +4770,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Nino a choisi le bac à sable. Il avait le seau. Il est allé vers la marelle. Bravo, Nino. C'est du bon travail. La craie de la marelle sèche, tout pâle. La chaîne de la balançoire se tait. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4650,7 +4910,16 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Nino a choisi le bac à sable.
+narrateur|Il avait le seau.
+narrateur|Il est allé vers la marelle.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La craie de la marelle sèche, tout pâle.
+narrateur|La chaîne de la balançoire se tait.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4678,7 +4947,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint Sami. La lumière est claire. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+          <t>Le cerceau jaune est dans l'herbe. Il est un peu chaud, au soleil. Une tige d'herbe passe au milieu. Nino a encore le seau. Il est près de le bac à sable. Le seau sonne, contre le cerceau. Tu as encore un mot, Nino ? Nino respire. J'ai écouté la maîtresse. Si malaise, je raconte. Bravo. Tu as écouté. Puis tu as raconté. C'est du bon travail, Nino. Merci, papa. Merci, maman. Le cerceau reste tout près.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4818,10 +5087,30 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint Sami. La lumière est claire. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr"/>
+          <t>narrateur|Le cerceau jaune est dans l'herbe.
+narrateur|Il est un peu chaud, au soleil.
+narrateur|Une tige d'herbe passe au milieu.
+narrateur|Nino a encore le seau.
+narrateur|Il est près de le bac à sable.
+narrateur|Le seau sonne, contre le cerceau.
+papa|Tu as encore un mot, Nino ?
+narrateur|Nino respire.
+enfant-m|J'ai écouté la maîtresse.
+enfant-m|Si malaise, je raconte.
+maman|Bravo.
+maman|Tu as écouté.
+maman|Puis tu as raconté.
+papa|C'est du bon travail, Nino.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Le cerceau reste tout près.</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>cerceau</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4846,7 +5135,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Nino a choisi le bac à sable. Il avait le seau. Il est allé vers le cerceau. Bravo, Nino. C'est du bon travail. Le cerceau jaune dort dans l'herbe. La chaîne de la balançoire se tait. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4986,7 +5275,16 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Nino a choisi le bac à sable.
+narrateur|Il avait le seau.
+narrateur|Il est allé vers le cerceau.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le cerceau jaune dort dans l'herbe.
+narrateur|La chaîne de la balançoire se tait.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5014,7 +5312,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a choisi le doudou. Le sol est un peu froid. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
+          <t>Nino prend le doudou gris. Une oreille est encore tiède. Il sent le cartable, un peu. Tu le serres, Nino ? Oui. Maman parle tout doux. Nino écoute jusqu'au bout. Le doudou est tiède. Bravo. Tu as écouté. Le doudou pose l'oreille sur le genou. Le doudou a un grain de sable, à l'oreille. On est encore près de le bac à sable. On écoute. Si malaise, on raconte.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5154,7 +5452,21 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo a choisi le doudou. Le sol est un peu froid. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
+          <t>narrateur|Nino prend le doudou gris.
+narrateur|Une oreille est encore tiède.
+narrateur|Il sent le cartable, un peu.
+maman|Tu le serres, Nino ?
+enfant-m|Oui.
+narrateur|Maman parle tout doux.
+narrateur|Nino écoute jusqu'au bout.
+enfant-m|Le doudou est tiède.
+papa|Bravo.
+papa|Tu as écouté.
+narrateur|Le doudou pose l'oreille sur le genou.
+narrateur|Le doudou a un grain de sable, à l'oreille.
+narrateur|On est encore près de le bac à sable.
+maman|On écoute.
+maman|Si malaise, on raconte.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5182,7 +5494,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois coins du parc attendent. Le banc, la marelle, ou le cerceau ? On écoute d'abord. Puis on raconte.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5350,7 +5662,10 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois coins du parc attendent.
+papa|Le banc, la marelle, ou le cerceau ?
+maman|On écoute d'abord.
+maman|Puis on raconte.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5378,7 +5693,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint Tom. Un vélo passe au loin. On se tient la main. Cette fin-là est celle de le bac à sable, le doudou et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+          <t>Le banc de bois est encore tiède. Le manteau jaune y fait un tas. Une flaque tient le ciel, tout bas. Nino a encore le doudou. Il est près de le bac à sable. Le doudou s'assoit sur le manteau jaune. Tu as encore un mot, Nino ? Nino respire. J'ai écouté la maîtresse. Si malaise, je raconte. Bravo. Tu as écouté. Puis tu as raconté. C'est du bon travail, Nino. Merci, papa. Merci, maman. Le banc reste tout près.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5518,10 +5833,30 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint Tom. Un vélo passe au loin. On se tient la main. Cette fin-là est celle de le bac à sable, le doudou et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr"/>
+          <t>narrateur|Le banc de bois est encore tiède.
+narrateur|Le manteau jaune y fait un tas.
+narrateur|Une flaque tient le ciel, tout bas.
+narrateur|Nino a encore le doudou.
+narrateur|Il est près de le bac à sable.
+narrateur|Le doudou s'assoit sur le manteau jaune.
+papa|Tu as encore un mot, Nino ?
+narrateur|Nino respire.
+enfant-m|J'ai écouté la maîtresse.
+enfant-m|Si malaise, je raconte.
+maman|Bravo.
+maman|Tu as écouté.
+maman|Puis tu as raconté.
+papa|C'est du bon travail, Nino.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Le banc reste tout près.</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>banc</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5546,7 +5881,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Nino a choisi le bac à sable. Il avait le doudou. Il est allé vers le banc. Bravo, Nino. C'est du bon travail. Le manteau jaune reste plié, tout calme. La chaîne de la balançoire se tait. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5686,7 +6021,16 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Nino a choisi le bac à sable.
+narrateur|Il avait le doudou.
+narrateur|Il est allé vers le banc.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le manteau jaune reste plié, tout calme.
+narrateur|La chaîne de la balançoire se tait.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5714,7 +6058,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint Léa. La lumière est claire. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+          <t>La marelle a des cases, à la craie. Une case est un peu effacée. La craie sent l'école, encore. Nino a encore le doudou. Il est près de le bac à sable. Le doudou pose l'oreille sur une case. Tu as encore un mot, Nino ? Nino respire. J'ai écouté la maîtresse. Si malaise, je raconte. Bravo. Tu as écouté. Puis tu as raconté. C'est du bon travail, Nino. Merci, papa. Merci, maman. La marelle reste tout près.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5854,10 +6198,30 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint Léa. La lumière est claire. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr"/>
+          <t>narrateur|La marelle a des cases, à la craie.
+narrateur|Une case est un peu effacée.
+narrateur|La craie sent l'école, encore.
+narrateur|Nino a encore le doudou.
+narrateur|Il est près de le bac à sable.
+narrateur|Le doudou pose l'oreille sur une case.
+papa|Tu as encore un mot, Nino ?
+narrateur|Nino respire.
+enfant-m|J'ai écouté la maîtresse.
+enfant-m|Si malaise, je raconte.
+maman|Bravo.
+maman|Tu as écouté.
+maman|Puis tu as raconté.
+papa|C'est du bon travail, Nino.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|La marelle reste tout près.</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>craie</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5882,7 +6246,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Nino a choisi le bac à sable. Il avait le doudou. Il est allé vers la marelle. Bravo, Nino. C'est du bon travail. La craie de la marelle sèche, tout pâle. La chaîne de la balançoire se tait. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6022,7 +6386,16 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Nino a choisi le bac à sable.
+narrateur|Il avait le doudou.
+narrateur|Il est allé vers la marelle.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La craie de la marelle sèche, tout pâle.
+narrateur|La chaîne de la balançoire se tait.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6050,7 +6423,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint Sami. Il y a des miettes sur la table. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+          <t>Le cerceau jaune est dans l'herbe. Il est un peu chaud, au soleil. Une tige d'herbe passe au milieu. Nino a encore le doudou. Il est près de le bac à sable. Le doudou regarde le cerceau, tout calme. Tu as encore un mot, Nino ? Nino respire. J'ai écouté la maîtresse. Si malaise, je raconte. Bravo. Tu as écouté. Puis tu as raconté. C'est du bon travail, Nino. Merci, papa. Merci, maman. Le cerceau reste tout près.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6190,10 +6563,30 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint Sami. Il y a des miettes sur la table. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr"/>
+          <t>narrateur|Le cerceau jaune est dans l'herbe.
+narrateur|Il est un peu chaud, au soleil.
+narrateur|Une tige d'herbe passe au milieu.
+narrateur|Nino a encore le doudou.
+narrateur|Il est près de le bac à sable.
+narrateur|Le doudou regarde le cerceau, tout calme.
+papa|Tu as encore un mot, Nino ?
+narrateur|Nino respire.
+enfant-m|J'ai écouté la maîtresse.
+enfant-m|Si malaise, je raconte.
+maman|Bravo.
+maman|Tu as écouté.
+maman|Puis tu as raconté.
+papa|C'est du bon travail, Nino.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Le cerceau reste tout près.</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>cerceau</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6218,7 +6611,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Nino a choisi le bac à sable. Il avait le doudou. Il est allé vers le cerceau. Bravo, Nino. C'est du bon travail. Le cerceau jaune dort dans l'herbe. La chaîne de la balançoire se tait. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6358,7 +6751,16 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Nino a choisi le bac à sable.
+narrateur|Il avait le doudou.
+narrateur|Il est allé vers le cerceau.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le cerceau jaune dort dans l'herbe.
+narrateur|La chaîne de la balançoire se tait.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6386,7 +6788,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Kenzo va vers le toboggan. On entend un oiseau. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Kenzo se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On range un objet. Je suis là. On reste ensemble.</t>
+          <t>Nino pose un pied sur la marche. Le métal du toboggan est tiède. Une feuille verte colle à la rampe. Ça sent l'herbe coupée, encore. Tu montes tout doux, Nino ? Oui, papa. Nino s'assoit en haut. Le galet appuie dans la poche. La maîtresse a parlé, ce matin. Nino a écouté jusqu'au bout. Puis quelqu'un a chuchoté, trop près. Le ventre se serre, tout petit. Papa. J'ai eu un malaise. Un secret, tout bas. Tu as bien fait de le dire. On écoute la maîtresse. Si malaise, on raconte à la maison. Je t'écoute, Nino. Bravo. C'est du bon travail. Nino glisse, tout lent. Le métal chante un tout petit ffft. Je raconte à papa et maman. Au parc aussi, on raconte.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6526,11 +6928,38 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo va vers le toboggan. On entend un oiseau. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Kenzo se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On range un objet.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr"/>
+          <t>narrateur|Nino pose un pied sur la marche.
+narrateur|Le métal du toboggan est tiède.
+narrateur|Une feuille verte colle à la rampe.
+narrateur|Ça sent l'herbe coupée, encore.
+papa|Tu montes tout doux, Nino ?
+enfant-m|Oui, papa.
+narrateur|Nino s'assoit en haut.
+narrateur|Le galet appuie dans la poche.
+narrateur|La maîtresse a parlé, ce matin.
+narrateur|Nino a écouté jusqu'au bout.
+narrateur|Puis quelqu'un a chuchoté, trop près.
+narrateur|Le ventre se serre, tout petit.
+enfant-m|Papa.
+enfant-m|J'ai eu un malaise.
+enfant-m|Un secret, tout bas.
+papa|Tu as bien fait de le dire.
+papa|On écoute la maîtresse.
+papa|Si malaise, on raconte à la maison.
+maman|Je t'écoute, Nino.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Nino glisse, tout lent.
+narrateur|Le métal chante un tout petit ffft.
+enfant-m|Je raconte à papa et maman.
+papa|Au parc aussi, on raconte.</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>toboggan</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6555,7 +6984,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>Nino a un malaise, en haut. Il raconte à qui ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6715,7 +7144,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>narrateur|Nino a un malaise, en haut.
+papa|Il raconte à qui ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6743,7 +7173,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo respire. Kenzo retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+          <t>Oui. À papa. À maman. À la maison. Nino pose les deux pieds dans l'herbe. J'ai raconté. Bravo. Tu as écouté, puis raconté. La feuille verte reste sur la rampe.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6887,7 +7317,15 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo respire. Kenzo retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+          <t>papa|Oui.
+papa|À papa.
+papa|À maman.
+papa|À la maison.
+narrateur|Nino pose les deux pieds dans l'herbe.
+enfant-m|J'ai raconté.
+maman|Bravo.
+maman|Tu as écouté, puis raconté.
+narrateur|La feuille verte reste sur la rampe.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6915,7 +7353,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Trois jouets attendent, dans l'herbe. Le ballon, le seau, ou le doudou ? On joue. On écoute. Et on raconte, si malaise.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7079,7 +7517,11 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|Trois jouets attendent, dans l'herbe.
+maman|Le ballon, le seau, ou le doudou ?
+papa|On joue.
+papa|On écoute.
+papa|Et on raconte, si malaise.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7107,7 +7549,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a choisi le ballon. Une feuille tombe. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On souffle doucement. papa n'est pas loin.</t>
+          <t>Nino prend le ballon rouge. Il sent le caoutchouc, un peu chaud. Une miette colle encore dessus. Tu veux le lancer, tout doux ? Oui, papa. Papa parle d'abord, tout calme. Nino écoute jusqu'au bout. Le ballon est chaud. Tu as écouté. Bravo. Le ballon fait un petit poum, dans l'herbe. Le ballon attend au pied du toboggan. On est encore près de le toboggan. On écoute. Si malaise, on raconte.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7247,10 +7689,28 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo a choisi le ballon. Une feuille tombe. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On souffle doucement. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr"/>
+          <t>narrateur|Nino prend le ballon rouge.
+narrateur|Il sent le caoutchouc, un peu chaud.
+narrateur|Une miette colle encore dessus.
+papa|Tu veux le lancer, tout doux ?
+enfant-m|Oui, papa.
+narrateur|Papa parle d'abord, tout calme.
+narrateur|Nino écoute jusqu'au bout.
+enfant-m|Le ballon est chaud.
+maman|Tu as écouté.
+maman|Bravo.
+narrateur|Le ballon fait un petit poum, dans l'herbe.
+narrateur|Le ballon attend au pied du toboggan.
+narrateur|On est encore près de le toboggan.
+maman|On écoute.
+maman|Si malaise, on raconte.</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>ballon</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7275,7 +7735,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois coins du parc attendent. Le banc, la marelle, ou le cerceau ? On écoute d'abord. Puis on raconte.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7443,7 +7903,10 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois coins du parc attendent.
+papa|Le banc, la marelle, ou le cerceau ?
+maman|On écoute d'abord.
+maman|Puis on raconte.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7471,7 +7934,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint Tom. L'eau coule, tout petit bruit. On range un objet. Cette fin-là est celle de le toboggan, le ballon et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+          <t>Le banc de bois est encore tiède. Le manteau jaune y fait un tas. Une flaque tient le ciel, tout bas. Nino a encore le ballon. Il est près de le toboggan. Le ballon roule du toboggan jusqu'au banc. Tu as encore un mot, Nino ? Nino respire. J'ai écouté la maîtresse. Si malaise, je raconte. Bravo. Tu as écouté. Puis tu as raconté. C'est du bon travail, Nino. Merci, papa. Merci, maman. Le banc reste tout près.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7611,10 +8074,30 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint Tom. L'eau coule, tout petit bruit. On range un objet. Cette fin-là est celle de le toboggan, le ballon et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr"/>
+          <t>narrateur|Le banc de bois est encore tiède.
+narrateur|Le manteau jaune y fait un tas.
+narrateur|Une flaque tient le ciel, tout bas.
+narrateur|Nino a encore le ballon.
+narrateur|Il est près de le toboggan.
+narrateur|Le ballon roule du toboggan jusqu'au banc.
+papa|Tu as encore un mot, Nino ?
+narrateur|Nino respire.
+enfant-m|J'ai écouté la maîtresse.
+enfant-m|Si malaise, je raconte.
+maman|Bravo.
+maman|Tu as écouté.
+maman|Puis tu as raconté.
+papa|C'est du bon travail, Nino.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Le banc reste tout près.</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>banc</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7639,7 +8122,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Nino a choisi le toboggan. Il avait le ballon. Il est allé vers le banc. Bravo, Nino. C'est du bon travail. Le manteau jaune reste plié, tout calme. La chaîne de la balançoire se tait. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7779,7 +8262,16 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Nino a choisi le toboggan.
+narrateur|Il avait le ballon.
+narrateur|Il est allé vers le banc.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le manteau jaune reste plié, tout calme.
+narrateur|La chaîne de la balançoire se tait.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7807,7 +8299,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint Léa. Un vélo passe au loin. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+          <t>La marelle a des cases, à la craie. Une case est un peu effacée. La craie sent l'école, encore. Nino a encore le ballon. Il est près de le toboggan. Le ballon s'arrête sur la première case. Tu as encore un mot, Nino ? Nino respire. J'ai écouté la maîtresse. Si malaise, je raconte. Bravo. Tu as écouté. Puis tu as raconté. C'est du bon travail, Nino. Merci, papa. Merci, maman. La marelle reste tout près.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7947,10 +8439,30 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint Léa. Un vélo passe au loin. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr"/>
+          <t>narrateur|La marelle a des cases, à la craie.
+narrateur|Une case est un peu effacée.
+narrateur|La craie sent l'école, encore.
+narrateur|Nino a encore le ballon.
+narrateur|Il est près de le toboggan.
+narrateur|Le ballon s'arrête sur la première case.
+papa|Tu as encore un mot, Nino ?
+narrateur|Nino respire.
+enfant-m|J'ai écouté la maîtresse.
+enfant-m|Si malaise, je raconte.
+maman|Bravo.
+maman|Tu as écouté.
+maman|Puis tu as raconté.
+papa|C'est du bon travail, Nino.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|La marelle reste tout près.</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>craie</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7975,7 +8487,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Nino a choisi le toboggan. Il avait le ballon. Il est allé vers la marelle. Bravo, Nino. C'est du bon travail. La craie de la marelle sèche, tout pâle. La chaîne de la balançoire se tait. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8115,7 +8627,16 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Nino a choisi le toboggan.
+narrateur|Il avait le ballon.
+narrateur|Il est allé vers la marelle.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La craie de la marelle sèche, tout pâle.
+narrateur|La chaîne de la balançoire se tait.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8143,7 +8664,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint Sami. La lumière est claire. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+          <t>Le cerceau jaune est dans l'herbe. Il est un peu chaud, au soleil. Une tige d'herbe passe au milieu. Nino a encore le ballon. Il est près de le toboggan. Le ballon traverse le cerceau, tout lent. Tu as encore un mot, Nino ? Nino respire. J'ai écouté la maîtresse. Si malaise, je raconte. Bravo. Tu as écouté. Puis tu as raconté. C'est du bon travail, Nino. Merci, papa. Merci, maman. Le cerceau reste tout près.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8283,10 +8804,30 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint Sami. La lumière est claire. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr"/>
+          <t>narrateur|Le cerceau jaune est dans l'herbe.
+narrateur|Il est un peu chaud, au soleil.
+narrateur|Une tige d'herbe passe au milieu.
+narrateur|Nino a encore le ballon.
+narrateur|Il est près de le toboggan.
+narrateur|Le ballon traverse le cerceau, tout lent.
+papa|Tu as encore un mot, Nino ?
+narrateur|Nino respire.
+enfant-m|J'ai écouté la maîtresse.
+enfant-m|Si malaise, je raconte.
+maman|Bravo.
+maman|Tu as écouté.
+maman|Puis tu as raconté.
+papa|C'est du bon travail, Nino.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Le cerceau reste tout près.</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>cerceau</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8311,7 +8852,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Nino a choisi le toboggan. Il avait le ballon. Il est allé vers le cerceau. Bravo, Nino. C'est du bon travail. Le cerceau jaune dort dans l'herbe. La chaîne de la balançoire se tait. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8451,7 +8992,16 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Nino a choisi le toboggan.
+narrateur|Il avait le ballon.
+narrateur|Il est allé vers le cerceau.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le cerceau jaune dort dans l'herbe.
+narrateur|La chaîne de la balançoire se tait.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8479,7 +9029,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a choisi le seau. L'eau coule, tout petit bruit. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
+          <t>Nino prend le seau bleu. Le plastique est un peu froid. Un peu de sable reste au fond. Tu veux remplir le seau ? Oui, maman. Maman parle d'abord. Nino écoute. Le seau est froid. Tu as écouté. Bravo, Nino. Le seau tapote le bois, tout fin. Le seau sonne un ding, contre le métal. On est encore près de le toboggan. On écoute. Si malaise, on raconte.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8619,10 +9169,28 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo a choisi le seau. L'eau coule, tout petit bruit. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr"/>
+          <t>narrateur|Nino prend le seau bleu.
+narrateur|Le plastique est un peu froid.
+narrateur|Un peu de sable reste au fond.
+maman|Tu veux remplir le seau ?
+enfant-m|Oui, maman.
+narrateur|Maman parle d'abord.
+narrateur|Nino écoute.
+enfant-m|Le seau est froid.
+papa|Tu as écouté.
+papa|Bravo, Nino.
+narrateur|Le seau tapote le bois, tout fin.
+narrateur|Le seau sonne un ding, contre le métal.
+narrateur|On est encore près de le toboggan.
+maman|On écoute.
+maman|Si malaise, on raconte.</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>seau</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8647,7 +9215,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois coins du parc attendent. Le banc, la marelle, ou le cerceau ? On écoute d'abord. Puis on raconte.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8815,7 +9383,10 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois coins du parc attendent.
+papa|Le banc, la marelle, ou le cerceau ?
+maman|On écoute d'abord.
+maman|Puis on raconte.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8843,7 +9414,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint Tom. Un vélo passe au loin. On range un objet. Cette fin-là est celle de le toboggan, le seau et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+          <t>Le banc de bois est encore tiède. Le manteau jaune y fait un tas. Une flaque tient le ciel, tout bas. Nino a encore le seau. Il est près de le toboggan. Le seau attend au pied du banc, tout bleu. Tu as encore un mot, Nino ? Nino respire. J'ai écouté la maîtresse. Si malaise, je raconte. Bravo. Tu as écouté. Puis tu as raconté. C'est du bon travail, Nino. Merci, papa. Merci, maman. Le banc reste tout près.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8983,10 +9554,30 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint Tom. Un vélo passe au loin. On range un objet. Cette fin-là est celle de le toboggan, le seau et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr"/>
+          <t>narrateur|Le banc de bois est encore tiède.
+narrateur|Le manteau jaune y fait un tas.
+narrateur|Une flaque tient le ciel, tout bas.
+narrateur|Nino a encore le seau.
+narrateur|Il est près de le toboggan.
+narrateur|Le seau attend au pied du banc, tout bleu.
+papa|Tu as encore un mot, Nino ?
+narrateur|Nino respire.
+enfant-m|J'ai écouté la maîtresse.
+enfant-m|Si malaise, je raconte.
+maman|Bravo.
+maman|Tu as écouté.
+maman|Puis tu as raconté.
+papa|C'est du bon travail, Nino.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Le banc reste tout près.</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>banc</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9011,7 +9602,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Nino a choisi le toboggan. Il avait le seau. Il est allé vers le banc. Bravo, Nino. C'est du bon travail. Le manteau jaune reste plié, tout calme. La chaîne de la balançoire se tait. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9151,7 +9742,16 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Nino a choisi le toboggan.
+narrateur|Il avait le seau.
+narrateur|Il est allé vers le banc.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le manteau jaune reste plié, tout calme.
+narrateur|La chaîne de la balançoire se tait.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9179,7 +9779,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint Léa. La lumière est claire. On dit merci. Cette fin-là est celle de le toboggan, le seau et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+          <t>La marelle a des cases, à la craie. Une case est un peu effacée. La craie sent l'école, encore. Nino a encore le seau. Il est près de le toboggan. Le seau pose sur la case du milieu. Tu as encore un mot, Nino ? Nino respire. J'ai écouté la maîtresse. Si malaise, je raconte. Bravo. Tu as écouté. Puis tu as raconté. C'est du bon travail, Nino. Merci, papa. Merci, maman. La marelle reste tout près.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9319,10 +9919,30 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint Léa. La lumière est claire. On dit merci. Cette fin-là est celle de le toboggan, le seau et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr"/>
+          <t>narrateur|La marelle a des cases, à la craie.
+narrateur|Une case est un peu effacée.
+narrateur|La craie sent l'école, encore.
+narrateur|Nino a encore le seau.
+narrateur|Il est près de le toboggan.
+narrateur|Le seau pose sur la case du milieu.
+papa|Tu as encore un mot, Nino ?
+narrateur|Nino respire.
+enfant-m|J'ai écouté la maîtresse.
+enfant-m|Si malaise, je raconte.
+maman|Bravo.
+maman|Tu as écouté.
+maman|Puis tu as raconté.
+papa|C'est du bon travail, Nino.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|La marelle reste tout près.</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>craie</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9347,7 +9967,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Nino a choisi le toboggan. Il avait le seau. Il est allé vers la marelle. Bravo, Nino. C'est du bon travail. La craie de la marelle sèche, tout pâle. La chaîne de la balançoire se tait. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9487,7 +10107,16 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Nino a choisi le toboggan.
+narrateur|Il avait le seau.
+narrateur|Il est allé vers la marelle.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La craie de la marelle sèche, tout pâle.
+narrateur|La chaîne de la balançoire se tait.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9515,7 +10144,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint Sami. Il y a des miettes sur la table. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+          <t>Le cerceau jaune est dans l'herbe. Il est un peu chaud, au soleil. Une tige d'herbe passe au milieu. Nino a encore le seau. Il est près de le toboggan. Le seau tient le cerceau, tout droit. Tu as encore un mot, Nino ? Nino respire. J'ai écouté la maîtresse. Si malaise, je raconte. Bravo. Tu as écouté. Puis tu as raconté. C'est du bon travail, Nino. Merci, papa. Merci, maman. Le cerceau reste tout près.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9655,10 +10284,30 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint Sami. Il y a des miettes sur la table. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr"/>
+          <t>narrateur|Le cerceau jaune est dans l'herbe.
+narrateur|Il est un peu chaud, au soleil.
+narrateur|Une tige d'herbe passe au milieu.
+narrateur|Nino a encore le seau.
+narrateur|Il est près de le toboggan.
+narrateur|Le seau tient le cerceau, tout droit.
+papa|Tu as encore un mot, Nino ?
+narrateur|Nino respire.
+enfant-m|J'ai écouté la maîtresse.
+enfant-m|Si malaise, je raconte.
+maman|Bravo.
+maman|Tu as écouté.
+maman|Puis tu as raconté.
+papa|C'est du bon travail, Nino.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Le cerceau reste tout près.</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>cerceau</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9683,7 +10332,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Nino a choisi le toboggan. Il avait le seau. Il est allé vers le cerceau. Bravo, Nino. C'est du bon travail. Le cerceau jaune dort dans l'herbe. La chaîne de la balançoire se tait. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9823,7 +10472,16 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Nino a choisi le toboggan.
+narrateur|Il avait le seau.
+narrateur|Il est allé vers le cerceau.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le cerceau jaune dort dans l'herbe.
+narrateur|La chaîne de la balançoire se tait.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9851,7 +10509,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a choisi le doudou. Un vélo passe au loin. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
+          <t>Nino prend le doudou gris. Une oreille est encore tiède. Il sent le cartable, un peu. Tu le serres, Nino ? Oui. Maman parle tout doux. Nino écoute jusqu'au bout. Le doudou est tiède. Bravo. Tu as écouté. Le doudou pose l'oreille sur le genou. Le doudou glisse un peu, sur la rampe. On est encore près de le toboggan. On écoute. Si malaise, on raconte.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9991,7 +10649,21 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo a choisi le doudou. Un vélo passe au loin. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
+          <t>narrateur|Nino prend le doudou gris.
+narrateur|Une oreille est encore tiède.
+narrateur|Il sent le cartable, un peu.
+maman|Tu le serres, Nino ?
+enfant-m|Oui.
+narrateur|Maman parle tout doux.
+narrateur|Nino écoute jusqu'au bout.
+enfant-m|Le doudou est tiède.
+papa|Bravo.
+papa|Tu as écouté.
+narrateur|Le doudou pose l'oreille sur le genou.
+narrateur|Le doudou glisse un peu, sur la rampe.
+narrateur|On est encore près de le toboggan.
+maman|On écoute.
+maman|Si malaise, on raconte.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr"/>
@@ -10019,7 +10691,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois coins du parc attendent. Le banc, la marelle, ou le cerceau ? On écoute d'abord. Puis on raconte.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10187,7 +10859,10 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois coins du parc attendent.
+papa|Le banc, la marelle, ou le cerceau ?
+maman|On écoute d'abord.
+maman|Puis on raconte.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10215,7 +10890,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint Tom. La lumière est claire. On range un objet. Cette fin-là est celle de le toboggan, le doudou et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+          <t>Le banc de bois est encore tiède. Le manteau jaune y fait un tas. Une flaque tient le ciel, tout bas. Nino a encore le doudou. Il est près de le toboggan. Le doudou rejoint le manteau, sur le banc. Tu as encore un mot, Nino ? Nino respire. J'ai écouté la maîtresse. Si malaise, je raconte. Bravo. Tu as écouté. Puis tu as raconté. C'est du bon travail, Nino. Merci, papa. Merci, maman. Le banc reste tout près.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10355,10 +11030,30 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint Tom. La lumière est claire. On range un objet. Cette fin-là est celle de le toboggan, le doudou et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr"/>
+          <t>narrateur|Le banc de bois est encore tiède.
+narrateur|Le manteau jaune y fait un tas.
+narrateur|Une flaque tient le ciel, tout bas.
+narrateur|Nino a encore le doudou.
+narrateur|Il est près de le toboggan.
+narrateur|Le doudou rejoint le manteau, sur le banc.
+papa|Tu as encore un mot, Nino ?
+narrateur|Nino respire.
+enfant-m|J'ai écouté la maîtresse.
+enfant-m|Si malaise, je raconte.
+maman|Bravo.
+maman|Tu as écouté.
+maman|Puis tu as raconté.
+papa|C'est du bon travail, Nino.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Le banc reste tout près.</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>banc</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10383,7 +11078,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Nino a choisi le toboggan. Il avait le doudou. Il est allé vers le banc. Bravo, Nino. C'est du bon travail. Le manteau jaune reste plié, tout calme. La chaîne de la balançoire se tait. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10523,7 +11218,16 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Nino a choisi le toboggan.
+narrateur|Il avait le doudou.
+narrateur|Il est allé vers le banc.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le manteau jaune reste plié, tout calme.
+narrateur|La chaîne de la balançoire se tait.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10551,7 +11255,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint Léa. Il y a des miettes sur la table. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+          <t>La marelle a des cases, à la craie. Une case est un peu effacée. La craie sent l'école, encore. Nino a encore le doudou. Il est près de le toboggan. Le doudou saute une case, tout doux. Tu as encore un mot, Nino ? Nino respire. J'ai écouté la maîtresse. Si malaise, je raconte. Bravo. Tu as écouté. Puis tu as raconté. C'est du bon travail, Nino. Merci, papa. Merci, maman. La marelle reste tout près.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10691,10 +11395,30 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint Léa. Il y a des miettes sur la table. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr"/>
+          <t>narrateur|La marelle a des cases, à la craie.
+narrateur|Une case est un peu effacée.
+narrateur|La craie sent l'école, encore.
+narrateur|Nino a encore le doudou.
+narrateur|Il est près de le toboggan.
+narrateur|Le doudou saute une case, tout doux.
+papa|Tu as encore un mot, Nino ?
+narrateur|Nino respire.
+enfant-m|J'ai écouté la maîtresse.
+enfant-m|Si malaise, je raconte.
+maman|Bravo.
+maman|Tu as écouté.
+maman|Puis tu as raconté.
+papa|C'est du bon travail, Nino.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|La marelle reste tout près.</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>craie</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10719,7 +11443,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Nino a choisi le toboggan. Il avait le doudou. Il est allé vers la marelle. Bravo, Nino. C'est du bon travail. La craie de la marelle sèche, tout pâle. La chaîne de la balançoire se tait. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10859,7 +11583,16 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Nino a choisi le toboggan.
+narrateur|Il avait le doudou.
+narrateur|Il est allé vers la marelle.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La craie de la marelle sèche, tout pâle.
+narrateur|La chaîne de la balançoire se tait.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10887,7 +11620,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint Sami. Un chat miaule une fois. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+          <t>Le cerceau jaune est dans l'herbe. Il est un peu chaud, au soleil. Une tige d'herbe passe au milieu. Nino a encore le doudou. Il est près de le toboggan. Le doudou passe la tête dans le cerceau. Tu as encore un mot, Nino ? Nino respire. J'ai écouté la maîtresse. Si malaise, je raconte. Bravo. Tu as écouté. Puis tu as raconté. C'est du bon travail, Nino. Merci, papa. Merci, maman. Le cerceau reste tout près.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11027,10 +11760,30 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint Sami. Un chat miaule une fois. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr"/>
+          <t>narrateur|Le cerceau jaune est dans l'herbe.
+narrateur|Il est un peu chaud, au soleil.
+narrateur|Une tige d'herbe passe au milieu.
+narrateur|Nino a encore le doudou.
+narrateur|Il est près de le toboggan.
+narrateur|Le doudou passe la tête dans le cerceau.
+papa|Tu as encore un mot, Nino ?
+narrateur|Nino respire.
+enfant-m|J'ai écouté la maîtresse.
+enfant-m|Si malaise, je raconte.
+maman|Bravo.
+maman|Tu as écouté.
+maman|Puis tu as raconté.
+papa|C'est du bon travail, Nino.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Le cerceau reste tout près.</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>cerceau</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11055,7 +11808,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Nino a choisi le toboggan. Il avait le doudou. Il est allé vers le cerceau. Bravo, Nino. C'est du bon travail. Le cerceau jaune dort dans l'herbe. La chaîne de la balançoire se tait. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11195,7 +11948,16 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Nino a choisi le toboggan.
+narrateur|Il avait le doudou.
+narrateur|Il est allé vers le cerceau.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le cerceau jaune dort dans l'herbe.
+narrateur|La chaîne de la balançoire se tait.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11223,7 +11985,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Kenzo va vers les balançoires. Ça sent le pain chaud. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Kenzo se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On dit merci. Je suis là. On reste ensemble.</t>
+          <t>Nino touche la chaîne tiède. Elle fait tic, contre le poteau. Le siège est en bois, un peu rêche. Un pigeon recule, tout près. Tu t'assoies, Nino ? Oui, maman. Nino pose les pieds dans l'herbe. L'herbe coupée colle aux chaussures. La craie de l'école reste au genou. Nino a écouté la maîtresse. Puis un chuchotement a serré le ventre. Maman. Papa. J'ai eu un malaise. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, tu viens nous le dire. Bravo, Nino. On t'écoute, toujours. La chaîne fait tic, plus doux. Le ventre se desserre. Je raconte à la maison. Ici aussi, Nino.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11363,11 +12125,36 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo va vers les balançoires. Ça sent le pain chaud. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Kenzo se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On dit merci.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr"/>
+          <t>narrateur|Nino touche la chaîne tiède.
+narrateur|Elle fait tic, contre le poteau.
+narrateur|Le siège est en bois, un peu rêche.
+narrateur|Un pigeon recule, tout près.
+maman|Tu t'assoies, Nino ?
+enfant-m|Oui, maman.
+narrateur|Nino pose les pieds dans l'herbe.
+narrateur|L'herbe coupée colle aux chaussures.
+narrateur|La craie de l'école reste au genou.
+narrateur|Nino a écouté la maîtresse.
+narrateur|Puis un chuchotement a serré le ventre.
+enfant-m|Maman.
+enfant-m|Papa.
+enfant-m|J'ai eu un malaise.
+maman|Tu as bien fait de raconter.
+papa|On écoute la maîtresse.
+papa|Si malaise, tu viens nous le dire.
+maman|Bravo, Nino.
+maman|On t'écoute, toujours.
+narrateur|La chaîne fait tic, plus doux.
+narrateur|Le ventre se desserre.
+enfant-m|Je raconte à la maison.
+papa|Ici aussi, Nino.</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>balancoire,oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11392,7 +12179,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>Le ventre de Nino s'est serré. On raconte à la maison ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11552,7 +12339,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>narrateur|Le ventre de Nino s'est serré.
+maman|On raconte à la maison ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11580,7 +12368,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo respire. Kenzo retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+          <t>Oui. On raconte à papa ou maman. À la maison. Nino serre la chaîne, tout doux. Je raconte. Bravo, Nino. On t'écoute. Le pigeon picore encore, plus loin.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11724,7 +12512,14 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo respire. Kenzo retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+          <t>maman|Oui.
+maman|On raconte à papa ou maman.
+maman|À la maison.
+narrateur|Nino serre la chaîne, tout doux.
+enfant-m|Je raconte.
+papa|Bravo, Nino.
+papa|On t'écoute.
+narrateur|Le pigeon picore encore, plus loin.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11752,7 +12547,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Trois jouets attendent, dans l'herbe. Le ballon, le seau, ou le doudou ? On joue. On écoute. Et on raconte, si malaise.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11916,7 +12711,11 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|Trois jouets attendent, dans l'herbe.
+maman|Le ballon, le seau, ou le doudou ?
+papa|On joue.
+papa|On écoute.
+papa|Et on raconte, si malaise.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11944,7 +12743,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a choisi le ballon. La lumière est claire. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On souffle doucement. papa n'est pas loin.</t>
+          <t>Nino prend le ballon rouge. Il sent le caoutchouc, un peu chaud. Une miette colle encore dessus. Tu veux le lancer, tout doux ? Oui, papa. Papa parle d'abord, tout calme. Nino écoute jusqu'au bout. Le ballon est chaud. Tu as écouté. Bravo. Le ballon fait un petit poum, dans l'herbe. Le ballon roule sous la balançoire. On est encore près de les balançoires. On écoute. Si malaise, on raconte.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12084,10 +12883,28 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo a choisi le ballon. La lumière est claire. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On souffle doucement. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr"/>
+          <t>narrateur|Nino prend le ballon rouge.
+narrateur|Il sent le caoutchouc, un peu chaud.
+narrateur|Une miette colle encore dessus.
+papa|Tu veux le lancer, tout doux ?
+enfant-m|Oui, papa.
+narrateur|Papa parle d'abord, tout calme.
+narrateur|Nino écoute jusqu'au bout.
+enfant-m|Le ballon est chaud.
+maman|Tu as écouté.
+maman|Bravo.
+narrateur|Le ballon fait un petit poum, dans l'herbe.
+narrateur|Le ballon roule sous la balançoire.
+narrateur|On est encore près de les balançoires.
+maman|On écoute.
+maman|Si malaise, on raconte.</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>ballon</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12112,7 +12929,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois coins du parc attendent. Le banc, la marelle, ou le cerceau ? On écoute d'abord. Puis on raconte.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12280,7 +13097,10 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois coins du parc attendent.
+papa|Le banc, la marelle, ou le cerceau ?
+maman|On écoute d'abord.
+maman|Puis on raconte.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12308,7 +13128,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint Tom. Un vélo passe au loin. On dit merci. Cette fin-là est celle de les balançoires, le ballon et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+          <t>Le banc de bois est encore tiède. Le manteau jaune y fait un tas. Une flaque tient le ciel, tout bas. Nino a encore le ballon. Il est près de les balançoires. Le ballon se gare sous le banc. Tu as encore un mot, Nino ? Nino respire. J'ai écouté la maîtresse. Si malaise, je raconte. Bravo. Tu as écouté. Puis tu as raconté. C'est du bon travail, Nino. Merci, papa. Merci, maman. Le banc reste tout près.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12448,10 +13268,30 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint Tom. Un vélo passe au loin. On dit merci. Cette fin-là est celle de les balançoires, le ballon et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr"/>
+          <t>narrateur|Le banc de bois est encore tiède.
+narrateur|Le manteau jaune y fait un tas.
+narrateur|Une flaque tient le ciel, tout bas.
+narrateur|Nino a encore le ballon.
+narrateur|Il est près de les balançoires.
+narrateur|Le ballon se gare sous le banc.
+papa|Tu as encore un mot, Nino ?
+narrateur|Nino respire.
+enfant-m|J'ai écouté la maîtresse.
+enfant-m|Si malaise, je raconte.
+maman|Bravo.
+maman|Tu as écouté.
+maman|Puis tu as raconté.
+papa|C'est du bon travail, Nino.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Le banc reste tout près.</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>banc</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12476,7 +13316,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Nino a choisi les balançoires. Il avait le ballon. Il est allé vers le banc. Bravo, Nino. C'est du bon travail. Le manteau jaune reste plié, tout calme. La chaîne de la balançoire se tait. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12616,7 +13456,16 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Nino a choisi les balançoires.
+narrateur|Il avait le ballon.
+narrateur|Il est allé vers le banc.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le manteau jaune reste plié, tout calme.
+narrateur|La chaîne de la balançoire se tait.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12644,7 +13493,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint Léa. La lumière est claire. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+          <t>La marelle a des cases, à la craie. Une case est un peu effacée. La craie sent l'école, encore. Nino a encore le ballon. Il est près de les balançoires. Le ballon fait poum, sur une case. Tu as encore un mot, Nino ? Nino respire. J'ai écouté la maîtresse. Si malaise, je raconte. Bravo. Tu as écouté. Puis tu as raconté. C'est du bon travail, Nino. Merci, papa. Merci, maman. La marelle reste tout près.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12784,10 +13633,30 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint Léa. La lumière est claire. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr"/>
+          <t>narrateur|La marelle a des cases, à la craie.
+narrateur|Une case est un peu effacée.
+narrateur|La craie sent l'école, encore.
+narrateur|Nino a encore le ballon.
+narrateur|Il est près de les balançoires.
+narrateur|Le ballon fait poum, sur une case.
+papa|Tu as encore un mot, Nino ?
+narrateur|Nino respire.
+enfant-m|J'ai écouté la maîtresse.
+enfant-m|Si malaise, je raconte.
+maman|Bravo.
+maman|Tu as écouté.
+maman|Puis tu as raconté.
+papa|C'est du bon travail, Nino.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|La marelle reste tout près.</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>craie</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12812,7 +13681,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Nino a choisi les balançoires. Il avait le ballon. Il est allé vers la marelle. Bravo, Nino. C'est du bon travail. La craie de la marelle sèche, tout pâle. La chaîne de la balançoire se tait. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12952,7 +13821,16 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Nino a choisi les balançoires.
+narrateur|Il avait le ballon.
+narrateur|Il est allé vers la marelle.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La craie de la marelle sèche, tout pâle.
+narrateur|La chaîne de la balançoire se tait.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12980,7 +13858,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint Sami. Il y a des miettes sur la table. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+          <t>Le cerceau jaune est dans l'herbe. Il est un peu chaud, au soleil. Une tige d'herbe passe au milieu. Nino a encore le ballon. Il est près de les balançoires. Le ballon et le cerceau se touchent. Tu as encore un mot, Nino ? Nino respire. J'ai écouté la maîtresse. Si malaise, je raconte. Bravo. Tu as écouté. Puis tu as raconté. C'est du bon travail, Nino. Merci, papa. Merci, maman. Le cerceau reste tout près.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13120,10 +13998,30 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint Sami. Il y a des miettes sur la table. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr"/>
+          <t>narrateur|Le cerceau jaune est dans l'herbe.
+narrateur|Il est un peu chaud, au soleil.
+narrateur|Une tige d'herbe passe au milieu.
+narrateur|Nino a encore le ballon.
+narrateur|Il est près de les balançoires.
+narrateur|Le ballon et le cerceau se touchent.
+papa|Tu as encore un mot, Nino ?
+narrateur|Nino respire.
+enfant-m|J'ai écouté la maîtresse.
+enfant-m|Si malaise, je raconte.
+maman|Bravo.
+maman|Tu as écouté.
+maman|Puis tu as raconté.
+papa|C'est du bon travail, Nino.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Le cerceau reste tout près.</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>cerceau</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13148,7 +14046,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Nino a choisi les balançoires. Il avait le ballon. Il est allé vers le cerceau. Bravo, Nino. C'est du bon travail. Le cerceau jaune dort dans l'herbe. La chaîne de la balançoire se tait. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13288,7 +14186,16 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Nino a choisi les balançoires.
+narrateur|Il avait le ballon.
+narrateur|Il est allé vers le cerceau.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le cerceau jaune dort dans l'herbe.
+narrateur|La chaîne de la balançoire se tait.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13316,7 +14223,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a choisi le seau. Il y a des miettes sur la table. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
+          <t>Nino prend le seau bleu. Le plastique est un peu froid. Un peu de sable reste au fond. Tu veux remplir le seau ? Oui, maman. Maman parle d'abord. Nino écoute. Le seau est froid. Tu as écouté. Bravo, Nino. Le seau tapote le bois, tout fin. Le seau tremble, quand la chaîne fait tic. On est encore près de les balançoires. On écoute. Si malaise, on raconte.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13456,10 +14363,28 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo a choisi le seau. Il y a des miettes sur la table. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr"/>
+          <t>narrateur|Nino prend le seau bleu.
+narrateur|Le plastique est un peu froid.
+narrateur|Un peu de sable reste au fond.
+maman|Tu veux remplir le seau ?
+enfant-m|Oui, maman.
+narrateur|Maman parle d'abord.
+narrateur|Nino écoute.
+enfant-m|Le seau est froid.
+papa|Tu as écouté.
+papa|Bravo, Nino.
+narrateur|Le seau tapote le bois, tout fin.
+narrateur|Le seau tremble, quand la chaîne fait tic.
+narrateur|On est encore près de les balançoires.
+maman|On écoute.
+maman|Si malaise, on raconte.</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>seau</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13484,7 +14409,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois coins du parc attendent. Le banc, la marelle, ou le cerceau ? On écoute d'abord. Puis on raconte.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13652,7 +14577,10 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois coins du parc attendent.
+papa|Le banc, la marelle, ou le cerceau ?
+maman|On écoute d'abord.
+maman|Puis on raconte.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13680,7 +14608,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint Tom. La lumière est claire. On dit merci. Cette fin-là est celle de les balançoires, le seau et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+          <t>Le banc de bois est encore tiède. Le manteau jaune y fait un tas. Une flaque tient le ciel, tout bas. Nino a encore le seau. Il est près de les balançoires. Le seau sonne un ding, contre le banc. Tu as encore un mot, Nino ? Nino respire. J'ai écouté la maîtresse. Si malaise, je raconte. Bravo. Tu as écouté. Puis tu as raconté. C'est du bon travail, Nino. Merci, papa. Merci, maman. Le banc reste tout près.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13820,10 +14748,30 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint Tom. La lumière est claire. On dit merci. Cette fin-là est celle de les balançoires, le seau et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr"/>
+          <t>narrateur|Le banc de bois est encore tiède.
+narrateur|Le manteau jaune y fait un tas.
+narrateur|Une flaque tient le ciel, tout bas.
+narrateur|Nino a encore le seau.
+narrateur|Il est près de les balançoires.
+narrateur|Le seau sonne un ding, contre le banc.
+papa|Tu as encore un mot, Nino ?
+narrateur|Nino respire.
+enfant-m|J'ai écouté la maîtresse.
+enfant-m|Si malaise, je raconte.
+maman|Bravo.
+maman|Tu as écouté.
+maman|Puis tu as raconté.
+papa|C'est du bon travail, Nino.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Le banc reste tout près.</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>banc</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13848,7 +14796,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Nino a choisi les balançoires. Il avait le seau. Il est allé vers le banc. Bravo, Nino. C'est du bon travail. Le manteau jaune reste plié, tout calme. La chaîne de la balançoire se tait. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13988,7 +14936,16 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Nino a choisi les balançoires.
+narrateur|Il avait le seau.
+narrateur|Il est allé vers le banc.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le manteau jaune reste plié, tout calme.
+narrateur|La chaîne de la balançoire se tait.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -14016,7 +14973,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint Léa. Il y a des miettes sur la table. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+          <t>La marelle a des cases, à la craie. Une case est un peu effacée. La craie sent l'école, encore. Nino a encore le seau. Il est près de les balançoires. Un grain de sable reste sur la marelle. Tu as encore un mot, Nino ? Nino respire. J'ai écouté la maîtresse. Si malaise, je raconte. Bravo. Tu as écouté. Puis tu as raconté. C'est du bon travail, Nino. Merci, papa. Merci, maman. La marelle reste tout près.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14156,10 +15113,30 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint Léa. Il y a des miettes sur la table. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr"/>
+          <t>narrateur|La marelle a des cases, à la craie.
+narrateur|Une case est un peu effacée.
+narrateur|La craie sent l'école, encore.
+narrateur|Nino a encore le seau.
+narrateur|Il est près de les balançoires.
+narrateur|Un grain de sable reste sur la marelle.
+papa|Tu as encore un mot, Nino ?
+narrateur|Nino respire.
+enfant-m|J'ai écouté la maîtresse.
+enfant-m|Si malaise, je raconte.
+maman|Bravo.
+maman|Tu as écouté.
+maman|Puis tu as raconté.
+papa|C'est du bon travail, Nino.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|La marelle reste tout près.</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>craie</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14184,7 +15161,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Nino a choisi les balançoires. Il avait le seau. Il est allé vers la marelle. Bravo, Nino. C'est du bon travail. La craie de la marelle sèche, tout pâle. La chaîne de la balançoire se tait. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14324,7 +15301,16 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Nino a choisi les balançoires.
+narrateur|Il avait le seau.
+narrateur|Il est allé vers la marelle.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La craie de la marelle sèche, tout pâle.
+narrateur|La chaîne de la balançoire se tait.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14352,7 +15338,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint Sami. Un chat miaule une fois. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+          <t>Le cerceau jaune est dans l'herbe. Il est un peu chaud, au soleil. Une tige d'herbe passe au milieu. Nino a encore le seau. Il est près de les balançoires. Le seau tremble dans le cerceau. Tu as encore un mot, Nino ? Nino respire. J'ai écouté la maîtresse. Si malaise, je raconte. Bravo. Tu as écouté. Puis tu as raconté. C'est du bon travail, Nino. Merci, papa. Merci, maman. Le cerceau reste tout près.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14492,10 +15478,30 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint Sami. Un chat miaule une fois. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr"/>
+          <t>narrateur|Le cerceau jaune est dans l'herbe.
+narrateur|Il est un peu chaud, au soleil.
+narrateur|Une tige d'herbe passe au milieu.
+narrateur|Nino a encore le seau.
+narrateur|Il est près de les balançoires.
+narrateur|Le seau tremble dans le cerceau.
+papa|Tu as encore un mot, Nino ?
+narrateur|Nino respire.
+enfant-m|J'ai écouté la maîtresse.
+enfant-m|Si malaise, je raconte.
+maman|Bravo.
+maman|Tu as écouté.
+maman|Puis tu as raconté.
+papa|C'est du bon travail, Nino.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Le cerceau reste tout près.</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>cerceau</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14520,7 +15526,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Nino a choisi les balançoires. Il avait le seau. Il est allé vers le cerceau. Bravo, Nino. C'est du bon travail. Le cerceau jaune dort dans l'herbe. La chaîne de la balançoire se tait. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14660,7 +15666,16 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Nino a choisi les balançoires.
+narrateur|Il avait le seau.
+narrateur|Il est allé vers le cerceau.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le cerceau jaune dort dans l'herbe.
+narrateur|La chaîne de la balançoire se tait.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14688,7 +15703,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a choisi le doudou. Un chat miaule une fois. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
+          <t>Nino prend le doudou gris. Une oreille est encore tiède. Il sent le cartable, un peu. Tu le serres, Nino ? Oui. Maman parle tout doux. Nino écoute jusqu'au bout. Le doudou est tiède. Bravo. Tu as écouté. Le doudou pose l'oreille sur le genou. Le doudou s'assoit sur le siège, tout calme. On est encore près de les balançoires. On écoute. Si malaise, on raconte.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14828,7 +15843,21 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo a choisi le doudou. Un chat miaule une fois. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
+          <t>narrateur|Nino prend le doudou gris.
+narrateur|Une oreille est encore tiède.
+narrateur|Il sent le cartable, un peu.
+maman|Tu le serres, Nino ?
+enfant-m|Oui.
+narrateur|Maman parle tout doux.
+narrateur|Nino écoute jusqu'au bout.
+enfant-m|Le doudou est tiède.
+papa|Bravo.
+papa|Tu as écouté.
+narrateur|Le doudou pose l'oreille sur le genou.
+narrateur|Le doudou s'assoit sur le siège, tout calme.
+narrateur|On est encore près de les balançoires.
+maman|On écoute.
+maman|Si malaise, on raconte.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -14856,7 +15885,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois coins du parc attendent. Le banc, la marelle, ou le cerceau ? On écoute d'abord. Puis on raconte.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15024,7 +16053,10 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois coins du parc attendent.
+papa|Le banc, la marelle, ou le cerceau ?
+maman|On écoute d'abord.
+maman|Puis on raconte.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15052,7 +16084,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint Tom. Il y a des miettes sur la table. On dit merci. Cette fin-là est celle de les balançoires, le doudou et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+          <t>Le banc de bois est encore tiède. Le manteau jaune y fait un tas. Une flaque tient le ciel, tout bas. Nino a encore le doudou. Il est près de les balançoires. Le doudou s'endort sur le manteau jaune. Tu as encore un mot, Nino ? Nino respire. J'ai écouté la maîtresse. Si malaise, je raconte. Bravo. Tu as écouté. Puis tu as raconté. C'est du bon travail, Nino. Merci, papa. Merci, maman. Le banc reste tout près.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15192,10 +16224,30 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint Tom. Il y a des miettes sur la table. On dit merci. Cette fin-là est celle de les balançoires, le doudou et Tom. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr"/>
+          <t>narrateur|Le banc de bois est encore tiède.
+narrateur|Le manteau jaune y fait un tas.
+narrateur|Une flaque tient le ciel, tout bas.
+narrateur|Nino a encore le doudou.
+narrateur|Il est près de les balançoires.
+narrateur|Le doudou s'endort sur le manteau jaune.
+papa|Tu as encore un mot, Nino ?
+narrateur|Nino respire.
+enfant-m|J'ai écouté la maîtresse.
+enfant-m|Si malaise, je raconte.
+maman|Bravo.
+maman|Tu as écouté.
+maman|Puis tu as raconté.
+papa|C'est du bon travail, Nino.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Le banc reste tout près.</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>banc</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15220,7 +16272,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Nino a choisi les balançoires. Il avait le doudou. Il est allé vers le banc. Bravo, Nino. C'est du bon travail. Le manteau jaune reste plié, tout calme. La chaîne de la balançoire se tait. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15360,7 +16412,16 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Nino a choisi les balançoires.
+narrateur|Il avait le doudou.
+narrateur|Il est allé vers le banc.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le manteau jaune reste plié, tout calme.
+narrateur|La chaîne de la balançoire se tait.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15388,7 +16449,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint Léa. Un chat miaule une fois. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+          <t>La marelle a des cases, à la craie. Une case est un peu effacée. La craie sent l'école, encore. Nino a encore le doudou. Il est près de les balançoires. Le doudou garde la case du ciel. Tu as encore un mot, Nino ? Nino respire. J'ai écouté la maîtresse. Si malaise, je raconte. Bravo. Tu as écouté. Puis tu as raconté. C'est du bon travail, Nino. Merci, papa. Merci, maman. La marelle reste tout près.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15528,10 +16589,30 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint Léa. Un chat miaule une fois. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Léa. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr"/>
+          <t>narrateur|La marelle a des cases, à la craie.
+narrateur|Une case est un peu effacée.
+narrateur|La craie sent l'école, encore.
+narrateur|Nino a encore le doudou.
+narrateur|Il est près de les balançoires.
+narrateur|Le doudou garde la case du ciel.
+papa|Tu as encore un mot, Nino ?
+narrateur|Nino respire.
+enfant-m|J'ai écouté la maîtresse.
+enfant-m|Si malaise, je raconte.
+maman|Bravo.
+maman|Tu as écouté.
+maman|Puis tu as raconté.
+papa|C'est du bon travail, Nino.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|La marelle reste tout près.</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>craie</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15556,7 +16637,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Nino a choisi les balançoires. Il avait le doudou. Il est allé vers la marelle. Bravo, Nino. C'est du bon travail. La craie de la marelle sèche, tout pâle. La chaîne de la balançoire se tait. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15696,7 +16777,16 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Nino a choisi les balançoires.
+narrateur|Il avait le doudou.
+narrateur|Il est allé vers la marelle.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La craie de la marelle sèche, tout pâle.
+narrateur|La chaîne de la balançoire se tait.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15724,7 +16814,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint Sami. Les chaussures font toc toc. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
+          <t>Le cerceau jaune est dans l'herbe. Il est un peu chaud, au soleil. Une tige d'herbe passe au milieu. Nino a encore le doudou. Il est près de les balançoires. Le doudou tient le cerceau, tout léger. Tu as encore un mot, Nino ? Nino respire. J'ai écouté la maîtresse. Si malaise, je raconte. Bravo. Tu as écouté. Puis tu as raconté. C'est du bon travail, Nino. Merci, papa. Merci, maman. Le cerceau reste tout près.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15864,10 +16954,30 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rejoint Sami. Les chaussures font toc toc. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Sami. Kenzo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Kenzo a entendu : écouter, si malaise raconter à la maison. Kenzo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr"/>
+          <t>narrateur|Le cerceau jaune est dans l'herbe.
+narrateur|Il est un peu chaud, au soleil.
+narrateur|Une tige d'herbe passe au milieu.
+narrateur|Nino a encore le doudou.
+narrateur|Il est près de les balançoires.
+narrateur|Le doudou tient le cerceau, tout léger.
+papa|Tu as encore un mot, Nino ?
+narrateur|Nino respire.
+enfant-m|J'ai écouté la maîtresse.
+enfant-m|Si malaise, je raconte.
+maman|Bravo.
+maman|Tu as écouté.
+maman|Puis tu as raconté.
+papa|C'est du bon travail, Nino.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Le cerceau reste tout près.</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>cerceau</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15892,7 +17002,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Nino a choisi les balançoires. Il avait le doudou. Il est allé vers le cerceau. Bravo, Nino. C'est du bon travail. Le cerceau jaune dort dans l'herbe. La chaîne de la balançoire se tait. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16032,7 +17142,16 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Nino a choisi les balançoires.
+narrateur|Il avait le doudou.
+narrateur|Il est allé vers le cerceau.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le cerceau jaune dort dans l'herbe.
+narrateur|La chaîne de la balançoire se tait.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16054,7 +17173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16148,6 +17267,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-033.xlsx
+++ b/stories/arbres/TREE-COL-033.xlsx
@@ -2753,17 +2753,17 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Nino roule le ballon jusqu'au banc, sable aux genoux. Il s'assoit. Le bois est tiède, comme la chaîne. Le ballon garde la place. Moi, je dis le mot. Il ouvre la bouche trop vite. Papa range le filet. Attends que le filet soit posé, puis toute la phrase. Nino attend. Le ballon ne bouge plus contre le pied. À l'école, près des crochets, une voix a parlé trop près. Ça m'a serré le ventre. La maîtresse m'a donné le galet. Nous t'avons entendu jusqu'au bout. Merci d'avoir attendu. Le galet repose sur une latte, un grain de sable dessus.</t>
+          <t>Nino roule le ballon jusqu'au banc, sable aux genoux. Il s'assoit. Le bois est tiède, comme la chaîne. Le ballon garde la place. Moi, je dis le mot. Il ouvre la bouche trop vite. Papa range le filet. Attends que le filet soit posé, puis toute la phrase. Nino attend. Le ballon ne bouge plus contre le pied. À l'école, près des crochets, une voix a parlé trop près. Ça m'a serré le ventre. La maîtresse m'a donné le galet. Nous t'avons entendu jusqu'au bout. Le galet repose sur une latte, un grain de sable dessus.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino roule le ballon jusqu'au banc, sable aux genoux. Il s'assoit. Le bois est tiède, comme la chaîne. Le ballon garde la place. Moi, je dis le mot. Il ouvre la bouche trop vite. Papa range le filet. Attends que le filet soit posé, puis toute la phrase. Nino attend. Le ballon ne bouge plus contre le pied. À l'école, près des crochets, une voix a parlé trop près. Ça m'a serré le ventre. La maîtresse m'a donné le galet. Nous t'avons entendu jusqu'au bout. Merci d'avoir attendu. Le galet repose sur une &lt;emphasis level="moderate"&gt;latte&lt;/emphasis&gt;, un grain de sable dessus.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino roule le ballon jusqu'au banc, sable aux genoux. Il s'assoit. Le bois est tiède, comme la chaîne. Le ballon garde la place. Moi, je dis le mot. Il ouvre la bouche trop vite. Papa range le filet. Attends que le filet soit posé, puis toute la phrase. Nino attend. Le ballon ne bouge plus contre le pied. À l'école, près des crochets, une voix a parlé trop près. Ça m'a serré le ventre. La maîtresse m'a donné le galet. Nous t'avons entendu jusqu'au bout. Le galet repose sur une &lt;emphasis level="moderate"&gt;latte&lt;/emphasis&gt;, un grain de sable dessus.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Nino roule le ballon jusqu'au banc, sable aux genoux. Il s'assoit. Le bois est tiède, comme la chaîne. Le ballon garde la place. Moi, je dis le mot. Il ouvre la bouche trop vite. Papa range le filet. Attends que le filet soit posé, puis toute la phrase. Nino attend. Le ballon ne bouge plus contre le pied. À l'école, près des crochets, une voix a parlé trop près. Ça m'a serré le ventre. La maîtresse m'a donné le galet. Nous t'avons entendu jusqu'au bout. Merci d'avoir attendu. Le galet repose sur une &lt;emphasis&gt;latte&lt;/emphasis&gt;, un grain de sable dessus. [pause]</t>
+          <t>Nino roule le ballon jusqu'au banc, sable aux genoux. Il s'assoit. Le bois est tiède, comme la chaîne. Le ballon garde la place. Moi, je dis le mot. Il ouvre la bouche trop vite. Papa range le filet. Attends que le filet soit posé, puis toute la phrase. Nino attend. Le ballon ne bouge plus contre le pied. À l'école, près des crochets, une voix a parlé trop près. Ça m'a serré le ventre. La maîtresse m'a donné le galet. Nous t'avons entendu jusqu'au bout. Le galet repose sur une &lt;emphasis&gt;latte&lt;/emphasis&gt;, un grain de sable dessus. [pause]</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
@@ -2911,7 +2911,6 @@
 enfant-m|Ça m'a serré le ventre.
 enfant-m|La maîtresse m'a donné le galet.
 papa|Nous t'avons entendu jusqu'au bout.
-papa|Merci d'avoir attendu.
 narrateur|Le galet repose sur une latte, un grain de sable dessus.</t>
         </is>
       </c>
@@ -3131,17 +3130,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Nino essuie le galet contre son short, puis le glisse. La poche sent le sable, et un peu de craie. Il rentre. Le mot aussi. Il parle en marchant. Papa ferme le cartable. On s'arrête. Tes pieds, puis tes mots. Nino s'arrête. Le ballon reste coincé sous son coude. Près des crochets, une voix a parlé trop près. Mon ventre s'est serré. La maîtresse m'a mis le galet là. Merci d'avoir posé tes pieds. Nous avons tout. Un grain de sable reste dans la couture de la poche.</t>
+          <t>Nino essuie le galet contre son short, puis le glisse. La poche sent le sable, et un peu de craie. Il rentre. Le mot aussi. Il parle en marchant. Papa ferme le cartable. On s'arrête. Tes pieds, puis tes mots. Nino s'arrête. Le ballon reste coincé sous son coude. Près des crochets, une voix a parlé trop près. Mon ventre s'est serré. La maîtresse m'a mis le galet là. Tes pieds sont posés. Nous avons toute la phrase. Un grain de sable reste dans la couture de la poche.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino essuie le galet contre son short, puis le glisse. La &lt;emphasis level="moderate"&gt;poche&lt;/emphasis&gt; sent le sable, et un peu de craie. Il rentre. Le mot aussi. Il parle en marchant. Papa ferme le cartable. On s'arrête. Tes pieds, puis tes mots. Nino s'arrête. Le ballon reste coincé sous son coude. Près des crochets, une voix a parlé trop près. Mon ventre s'est serré. La maîtresse m'a mis le galet là. Merci d'avoir posé tes pieds. Nous avons tout. Un grain de sable reste dans la couture de la poche.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino essuie le galet contre son short, puis le glisse. La &lt;emphasis level="moderate"&gt;poche&lt;/emphasis&gt; sent le sable, et un peu de craie. Il rentre. Le mot aussi. Il parle en marchant. Papa ferme le cartable. On s'arrête. Tes pieds, puis tes mots. Nino s'arrête. Le ballon reste coincé sous son coude. Près des crochets, une voix a parlé trop près. Mon ventre s'est serré. La maîtresse m'a mis le galet là. Tes pieds sont posés. Nous avons toute la phrase. Un grain de sable reste dans la couture de la poche.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Nino essuie le galet contre son short, puis le glisse. La &lt;emphasis&gt;poche&lt;/emphasis&gt; sent le sable, et un peu de craie. Il rentre. Le mot aussi. Il parle en marchant. Papa ferme le cartable. On s'arrête. Tes pieds, puis tes mots. Nino s'arrête. Le ballon reste coincé sous son coude. Près des crochets, une voix a parlé trop près. Mon ventre s'est serré. La maîtresse m'a mis le galet là. Merci d'avoir posé tes pieds. Nous avons tout. Un grain de sable reste dans la couture de la poche. [pause]</t>
+          <t>Nino essuie le galet contre son short, puis le glisse. La &lt;emphasis&gt;poche&lt;/emphasis&gt; sent le sable, et un peu de craie. Il rentre. Le mot aussi. Il parle en marchant. Papa ferme le cartable. On s'arrête. Tes pieds, puis tes mots. Nino s'arrête. Le ballon reste coincé sous son coude. Près des crochets, une voix a parlé trop près. Mon ventre s'est serré. La maîtresse m'a mis le galet là. Tes pieds sont posés. Nous avons toute la phrase. Un grain de sable reste dans la couture de la poche. [pause]</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -3288,8 +3287,8 @@
 enfant-m|Près des crochets, une voix a parlé trop près.
 enfant-m|Mon ventre s'est serré.
 enfant-m|La maîtresse m'a mis le galet là.
-maman|Merci d'avoir posé tes pieds.
-maman|Nous avons tout.
+maman|Tes pieds sont posés.
+maman|Nous avons toute la phrase.
 narrateur|Un grain de sable reste dans la couture de la poche.</t>
         </is>
       </c>
@@ -4283,17 +4282,17 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Nino porte le seau jusqu'au banc, deux mains sur l'anse. Il le pose. Un peu de sable fuit par le fond troué. Le galet est au fond. Le mot est pour le banc. Il s'assoit trop vite. Le seau vacille. On pose l'anse, puis on parle. D'accord ? Nino pose l'anse. Il souffle par le nez. Près des crochets, une voix a parlé trop près. La maîtresse m'a donné le galet. Mon ventre s'est serré. Merci d'avoir posé l'anse. Nous t'écoutions. Le galet reste dans le seau, au pied de la latte.</t>
+          <t>Nino porte le seau jusqu'au banc, deux mains sur l'anse. Il le pose. Un peu de sable fuit par le fond troué. Le galet est au fond. Le mot est pour le banc. Il s'assoit trop vite. Le seau vacille. On pose l'anse, puis on parle. D'accord ? Nino pose l'anse. Il souffle par le nez. Près des crochets, une voix a parlé trop près. La maîtresse m'a donné le galet. Mon ventre s'est serré. L'anse est posée. Nous t'écoutions. Le galet reste dans le seau, au pied de la latte.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino porte le seau jusqu'au banc, deux mains sur l'&lt;emphasis level="moderate"&gt;anse&lt;/emphasis&gt;. Il le pose. Un peu de sable fuit par le fond troué. Le galet est au fond. Le mot est pour le banc. Il s'assoit trop vite. Le seau vacille. On pose l'anse, puis on parle. D'accord ? Nino pose l'anse. Il souffle par le nez. Près des crochets, une voix a parlé trop près. La maîtresse m'a donné le galet. Mon ventre s'est serré. Merci d'avoir posé l'anse. Nous t'écoutions. Le galet reste dans le seau, au pied de la latte.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino porte le seau jusqu'au banc, deux mains sur l'&lt;emphasis level="moderate"&gt;anse&lt;/emphasis&gt;. Il le pose. Un peu de sable fuit par le fond troué. Le galet est au fond. Le mot est pour le banc. Il s'assoit trop vite. Le seau vacille. On pose l'anse, puis on parle. D'accord ? Nino pose l'anse. Il souffle par le nez. Près des crochets, une voix a parlé trop près. La maîtresse m'a donné le galet. Mon ventre s'est serré. L'anse est posée. Nous t'écoutions. Le galet reste dans le seau, au pied de la latte.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Nino porte le seau jusqu'au banc, deux mains sur l'&lt;emphasis&gt;anse&lt;/emphasis&gt;. Il le pose. Un peu de sable fuit par le fond troué. Le galet est au fond. Le mot est pour le banc. Il s'assoit trop vite. Le seau vacille. On pose l'anse, puis on parle. D'accord ? Nino pose l'anse. Il souffle par le nez. Près des crochets, une voix a parlé trop près. La maîtresse m'a donné le galet. Mon ventre s'est serré. Merci d'avoir posé l'anse. Nous t'écoutions. Le galet reste dans le seau, au pied de la latte. [pause]</t>
+          <t>Nino porte le seau jusqu'au banc, deux mains sur l'&lt;emphasis&gt;anse&lt;/emphasis&gt;. Il le pose. Un peu de sable fuit par le fond troué. Le galet est au fond. Le mot est pour le banc. Il s'assoit trop vite. Le seau vacille. On pose l'anse, puis on parle. D'accord ? Nino pose l'anse. Il souffle par le nez. Près des crochets, une voix a parlé trop près. La maîtresse m'a donné le galet. Mon ventre s'est serré. L'anse est posée. Nous t'écoutions. Le galet reste dans le seau, au pied de la latte. [pause]</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -4441,7 +4440,7 @@
 enfant-m|Près des crochets, une voix a parlé trop près.
 enfant-m|La maîtresse m'a donné le galet.
 enfant-m|Mon ventre s'est serré.
-maman|Merci d'avoir posé l'anse.
+maman|L'anse est posée.
 maman|Nous t'écoutions.
 narrateur|Le galet reste dans le seau, au pied de la latte.</t>
         </is>
@@ -5039,17 +5038,17 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Nino tend le seau. Maman avance la paume au-dessus. Le galet tombe, un poids court, dans sa main. Il est à toi le temps du mot. Du sable coule entre ses doigts, fin, blond. On souffle le sable, puis Nino parle. D'accord ? Nino hoche. Il attend le dernier grain. Une voix trop près, aux crochets. Mon ventre s'est serré. La maîtresse a dit de vous le donner, avec la pierre. Merci. Ma paume a le galet. Mes oreilles ont le mot. Un halo de poussière blonde reste sur sa peau.</t>
+          <t>Nino tend le seau. Maman avance la paume au-dessus. Le galet tombe, un poids court, dans sa main. Il est à toi le temps du mot. Du sable coule entre ses doigts, fin, blond. On souffle le sable, puis Nino parle. D'accord ? Nino hoche. Il attend le dernier grain. Une voix trop près, aux crochets. Mon ventre s'est serré. La maîtresse a dit de vous le donner, avec la pierre. Ma paume a le galet. Mes oreilles ont le mot. Un halo de poussière blonde reste sur sa peau.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino tend le seau. Maman avance la paume au-dessus. Le galet tombe, un poids court, dans sa main. Il est à toi le temps du mot. Du sable coule entre ses doigts, fin, blond. On souffle le sable, puis Nino parle. D'accord ? Nino hoche. Il attend le dernier &lt;emphasis level="moderate"&gt;grain&lt;/emphasis&gt;. Une voix trop près, aux crochets. Mon ventre s'est serré. La maîtresse a dit de vous le donner, avec la pierre. Merci. Ma paume a le galet. Mes oreilles ont le mot. Un halo de poussière blonde reste sur sa peau.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino tend le seau. Maman avance la paume au-dessus. Le galet tombe, un poids court, dans sa main. Il est à toi le temps du mot. Du sable coule entre ses doigts, fin, blond. On souffle le sable, puis Nino parle. D'accord ? Nino hoche. Il attend le dernier &lt;emphasis level="moderate"&gt;grain&lt;/emphasis&gt;. Une voix trop près, aux crochets. Mon ventre s'est serré. La maîtresse a dit de vous le donner, avec la pierre. Ma paume a le galet. Mes oreilles ont le mot. Un halo de poussière blonde reste sur sa peau.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Nino tend le seau. Maman avance la paume au-dessus. Le galet tombe, un poids court, dans sa main. Il est à toi le temps du mot. Du sable coule entre ses doigts, fin, blond. On souffle le sable, puis Nino parle. D'accord ? Nino hoche. Il attend le dernier &lt;emphasis&gt;grain&lt;/emphasis&gt;. Une voix trop près, aux crochets. Mon ventre s'est serré. La maîtresse a dit de vous le donner, avec la pierre. Merci. Ma paume a le galet. Mes oreilles ont le mot. Un halo de poussière blonde reste sur sa peau. [pause]</t>
+          <t>Nino tend le seau. Maman avance la paume au-dessus. Le galet tombe, un poids court, dans sa main. Il est à toi le temps du mot. Du sable coule entre ses doigts, fin, blond. On souffle le sable, puis Nino parle. D'accord ? Nino hoche. Il attend le dernier &lt;emphasis&gt;grain&lt;/emphasis&gt;. Une voix trop près, aux crochets. Mon ventre s'est serré. La maîtresse a dit de vous le donner, avec la pierre. Ma paume a le galet. Mes oreilles ont le mot. Un halo de poussière blonde reste sur sa peau. [pause]</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
@@ -5195,7 +5194,6 @@
 enfant-m|Une voix trop près, aux crochets.
 enfant-m|Mon ventre s'est serré.
 enfant-m|La maîtresse a dit de vous le donner, avec la pierre.
-maman|Merci.
 maman|Ma paume a le galet.
 maman|Mes oreilles ont le mot.
 narrateur|Un halo de poussière blonde reste sur sa peau.</t>
@@ -6566,17 +6564,17 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Nino met le doudou à cheval sur son bras, comme un témoin. Il dépose le galet dans la paume de papa, sable et tout. Toi tu le tiens. Moi je parle. Papa souffle le grain. Maman range une lanière. La lanière est bouclée. Nous t'écoutons. Nino attendait ce bouclage, lèvres serrées. Une voix trop près, aux crochets. Ça m'a serré. Elle m'a donné le galet. Le doudou a entendu, lui aussi. Ma paume a la pierre. Merci d'avoir attendu la lanière. Le doudou penche vers la main, museau contre le pouce.</t>
+          <t>Nino met le doudou à cheval sur son bras, comme un témoin. Il dépose le galet dans la paume de papa, sable et tout. Toi tu le tiens. Moi je parle. Papa souffle le grain. Maman range une lanière. La lanière est bouclée. Nous t'écoutons. Nino attendait ce bouclage, lèvres serrées. Une voix trop près, aux crochets. Ça m'a serré. Elle m'a donné le galet. Le doudou a entendu, lui aussi. Ma paume a la pierre. La lanière est bouclée. Le doudou penche vers la main, museau contre le pouce.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino met le doudou à cheval sur son bras, comme un témoin. Il dépose le galet dans la paume de papa, sable et tout. Toi tu le tiens. Moi je parle. Papa souffle le grain. Maman range une &lt;emphasis level="moderate"&gt;lanière&lt;/emphasis&gt;. La lanière est bouclée. Nous t'écoutons. Nino attendait ce bouclage, lèvres serrées. Une voix trop près, aux crochets. Ça m'a serré. Elle m'a donné le galet. Le doudou a entendu, lui aussi. Ma paume a la pierre. Merci d'avoir attendu la lanière. Le doudou penche vers la main, museau contre le pouce.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino met le doudou à cheval sur son bras, comme un témoin. Il dépose le galet dans la paume de papa, sable et tout. Toi tu le tiens. Moi je parle. Papa souffle le grain. Maman range une &lt;emphasis level="moderate"&gt;lanière&lt;/emphasis&gt;. La lanière est bouclée. Nous t'écoutons. Nino attendait ce bouclage, lèvres serrées. Une voix trop près, aux crochets. Ça m'a serré. Elle m'a donné le galet. Le doudou a entendu, lui aussi. Ma paume a la pierre. La lanière est bouclée. Le doudou penche vers la main, museau contre le pouce.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Nino met le doudou à cheval sur son bras, comme un témoin. Il dépose le galet dans la paume de papa, sable et tout. Toi tu le tiens. Moi je parle. Papa souffle le grain. Maman range une &lt;emphasis&gt;lanière&lt;/emphasis&gt;. La lanière est bouclée. Nous t'écoutons. Nino attendait ce bouclage, lèvres serrées. Une voix trop près, aux crochets. Ça m'a serré. Elle m'a donné le galet. Le doudou a entendu, lui aussi. Ma paume a la pierre. Merci d'avoir attendu la lanière. Le doudou penche vers la main, museau contre le pouce. [pause]</t>
+          <t>Nino met le doudou à cheval sur son bras, comme un témoin. Il dépose le galet dans la paume de papa, sable et tout. Toi tu le tiens. Moi je parle. Papa souffle le grain. Maman range une &lt;emphasis&gt;lanière&lt;/emphasis&gt;. La lanière est bouclée. Nous t'écoutons. Nino attendait ce bouclage, lèvres serrées. Une voix trop près, aux crochets. Ça m'a serré. Elle m'a donné le galet. Le doudou a entendu, lui aussi. Ma paume a la pierre. La lanière est bouclée. Le doudou penche vers la main, museau contre le pouce. [pause]</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -6724,7 +6722,7 @@
 enfant-m|Elle m'a donné le galet.
 enfant-m|Le doudou a entendu, lui aussi.
 papa|Ma paume a la pierre.
-papa|Merci d'avoir attendu la lanière.
+papa|La lanière est bouclée.
 narrateur|Le doudou penche vers la main, museau contre le pouce.</t>
         </is>
       </c>
@@ -7327,17 +7325,17 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Il attend que les visages se lèvent. Maman plisse les yeux. Papa lâche la fermeture. Nous te voyons, minuscule, en haut du métal. Le mot n'a pas dévalé. Il est resté avec moi. Merci d'avoir attendu nos visages. Le palier vibre un peu, puis s'arrête. Le galet tient, gris, entre deux genoux.</t>
+          <t>Oui. Il attend que les visages se lèvent. Maman plisse les yeux. Papa lâche la fermeture. Nous te voyons, là-haut, sur le métal. Le mot n'a pas dévalé. Il est resté avec moi. Merci d'avoir attendu nos visages. Le palier vibre un peu, puis s'arrête. Le galet tient, gris, entre deux genoux.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Oui. Il attend que les &lt;emphasis level="moderate"&gt;visages&lt;/emphasis&gt; se lèvent. Maman plisse les yeux. Papa lâche la fermeture. Nous te voyons, minuscule, en haut du métal. Le mot n'a pas dévalé. Il est resté avec moi. Merci d'avoir attendu nos visages. Le palier vibre un peu, puis s'arrête. Le galet tient, gris, entre deux genoux.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Oui. Il attend que les &lt;emphasis level="moderate"&gt;visages&lt;/emphasis&gt; se lèvent. Maman plisse les yeux. Papa lâche la fermeture. Nous te voyons, là-haut, sur le métal. Le mot n'a pas dévalé. Il est resté avec moi. Merci d'avoir attendu nos visages. Le palier vibre un peu, puis s'arrête. Le galet tient, gris, entre deux genoux.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Il attend que les &lt;emphasis&gt;visages&lt;/emphasis&gt; se lèvent. Maman plisse les yeux. Papa lâche la fermeture. Nous te voyons, minuscule, en haut du métal. Le mot n'a pas dévalé. Il est resté avec moi. Merci d'avoir attendu nos visages. Le palier vibre un peu, puis s'arrête. Le galet tient, gris, entre deux genoux. [pause]</t>
+          <t>Oui. Il attend que les &lt;emphasis&gt;visages&lt;/emphasis&gt; se lèvent. Maman plisse les yeux. Papa lâche la fermeture. Nous te voyons, là-haut, sur le métal. Le mot n'a pas dévalé. Il est resté avec moi. Merci d'avoir attendu nos visages. Le palier vibre un peu, puis s'arrête. Le galet tient, gris, entre deux genoux. [pause]</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
@@ -7475,7 +7473,7 @@
 papa|Il attend que les visages se lèvent.
 narrateur|Maman plisse les yeux.
 narrateur|Papa lâche la fermeture.
-maman|Nous te voyons, minuscule, en haut du métal.
+maman|Nous te voyons, là-haut, sur le métal.
 enfant-m|Le mot n'a pas dévalé.
 enfant-m|Il est resté avec moi.
 papa|Merci d'avoir attendu nos visages.
@@ -8099,17 +8097,17 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Nino descend, le ballon sous le bras, le galet au poing. Ils rejoignent le banc, face à la pente tiède. Le ballon a dévalé tout seul. Le mot, non. Il s'assoit. Le bois craque. Papa souffle. Le craquement d'abord. Après, ta phrase. Nino attend que le bois se taise. En haut, j'ai eu le ventre serré, comme aux crochets. Une voix trop près. La maîtresse m'a donné le galet. Merci d'avoir attendu le banc. Nous avons tout. Le ballon rouge cale un pied de banc, pour ne plus rouler.</t>
+          <t>Nino descend, le ballon sous le bras, le galet au poing. Ils rejoignent le banc, face à la pente tiède. Le ballon a dévalé tout seul. Le mot, non. Il s'assoit. Le bois craque. Papa souffle. Le craquement d'abord. Après, ta phrase. Nino attend que le bois se taise. En haut, j'ai eu le ventre serré, comme aux crochets. Une voix trop près. La maîtresse m'a donné le galet. Le banc s'est tu. Nous avons toute la phrase. Le ballon rouge cale un pied de banc, pour ne plus rouler.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino descend, le ballon sous le bras, le galet au poing. Ils rejoignent le banc, face à la pente tiède. Le ballon a dévalé tout seul. Le mot, non. Il s'assoit. Le bois craque. Papa souffle. Le craquement d'abord. Après, ta phrase. Nino attend que le bois se taise. En haut, j'ai eu le ventre serré, comme aux crochets. Une voix trop près. La maîtresse m'a donné le galet. Merci d'avoir attendu le banc. Nous avons tout. Le ballon rouge cale un pied de banc, pour ne plus rouler.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino descend, le ballon sous le bras, le galet au poing. Ils rejoignent le banc, face à la pente tiède. Le ballon a dévalé tout seul. Le mot, non. Il s'assoit. Le bois craque. Papa souffle. Le craquement d'abord. Après, ta phrase. Nino attend que le bois se taise. En haut, j'ai eu le ventre serré, comme aux crochets. Une voix trop près. La maîtresse m'a donné le galet. Le banc s'est tu. Nous avons toute la phrase. Le ballon rouge cale un pied de banc, pour ne plus rouler.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Nino descend, le ballon sous le bras, le galet au poing. Ils rejoignent le banc, face à la pente tiède. Le ballon a dévalé tout seul. Le mot, non. Il s'assoit. Le bois craque. Papa souffle. Le craquement d'abord. Après, ta phrase. Nino attend que le bois se taise. En haut, j'ai eu le ventre serré, comme aux crochets. Une voix trop près. La maîtresse m'a donné le galet. Merci d'avoir attendu le banc. Nous avons tout. Le ballon rouge cale un pied de banc, pour ne plus rouler. [pause]</t>
+          <t>Nino descend, le ballon sous le bras, le galet au poing. Ils rejoignent le banc, face à la pente tiède. Le ballon a dévalé tout seul. Le mot, non. Il s'assoit. Le bois craque. Papa souffle. Le craquement d'abord. Après, ta phrase. Nino attend que le bois se taise. En haut, j'ai eu le ventre serré, comme aux crochets. Une voix trop près. La maîtresse m'a donné le galet. Le banc s'est tu. Nous avons toute la phrase. Le ballon rouge cale un pied de banc, pour ne plus rouler. [pause]</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
@@ -8256,8 +8254,8 @@
 enfant-m|En haut, j'ai eu le ventre serré, comme aux crochets.
 enfant-m|Une voix trop près.
 enfant-m|La maîtresse m'a donné le galet.
-maman|Merci d'avoir attendu le banc.
-maman|Nous avons tout.
+maman|Le banc s'est tu.
+maman|Nous avons toute la phrase.
 narrateur|Le ballon rouge cale un pied de banc, pour ne plus rouler.</t>
         </is>
       </c>
@@ -8857,17 +8855,17 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Maman lève les mains au bas de la pente, paumes ouvertes. Nino, en haut, penche le galet. Il ne le jette pas. Je le pose. Je ne le lance pas. Il descend deux marches. Le galet rejoint la paume. Le ballon attend dans l'herbe, témoin rond. La pierre est arrivée. Maintenant le mot, s'il te plaît ? Nino pose les deux pieds dans l'herbe avant de parler. Une voix trop près, aux crochets. Mon ventre s'est serré. La maîtresse a dit : tu le donnes, ce soir. Tu l'as donné. Merci d'avoir posé tes pieds.</t>
+          <t>Maman lève les mains au bas de la pente, paumes ouvertes. Nino, en haut, penche le galet. Il ne le jette pas. Je le pose. Je ne le lance pas. Il descend deux marches. Le galet rejoint la paume. Le ballon attend dans l'herbe, témoin rond. La pierre est arrivée. Maintenant le mot, s'il te plaît ? Nino pose les deux pieds dans l'herbe avant de parler. Une voix trop près, aux crochets. Mon ventre s'est serré. La maîtresse a dit : tu le donnes, ce soir. Tu l'as donné. Tes pieds sont dans l'herbe.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman lève les mains au bas de la pente, paumes ouvertes. Nino, en haut, penche le galet. Il ne le jette pas. Je le pose. Je ne le lance pas. Il descend deux marches. Le galet rejoint la paume. Le ballon attend dans l'herbe, témoin rond. La pierre est arrivée. Maintenant le mot, s'il te plaît ? Nino pose les deux pieds dans l'herbe avant de parler. Une voix trop près, aux crochets. Mon ventre s'est serré. La maîtresse a dit : tu le donnes, ce soir. Tu l'as donné. Merci d'avoir posé tes pieds.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman lève les mains au bas de la pente, paumes ouvertes. Nino, en haut, penche le galet. Il ne le jette pas. Je le pose. Je ne le lance pas. Il descend deux marches. Le galet rejoint la paume. Le ballon attend dans l'herbe, témoin rond. La pierre est arrivée. Maintenant le mot, s'il te plaît ? Nino pose les deux pieds dans l'herbe avant de parler. Une voix trop près, aux crochets. Mon ventre s'est serré. La maîtresse a dit : tu le donnes, ce soir. Tu l'as donné. Tes pieds sont dans l'herbe.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Maman lève les mains au bas de la pente, paumes ouvertes. Nino, en haut, penche le galet. Il ne le jette pas. Je le pose. Je ne le lance pas. Il descend deux marches. Le galet rejoint la paume. Le ballon attend dans l'herbe, témoin rond. La pierre est arrivée. Maintenant le mot, s'il te plaît ? Nino pose les deux pieds dans l'herbe avant de parler. Une voix trop près, aux crochets. Mon ventre s'est serré. La maîtresse a dit : tu le donnes, ce soir. Tu l'as donné. Merci d'avoir posé tes pieds. [pause]</t>
+          <t>Maman lève les mains au bas de la pente, paumes ouvertes. Nino, en haut, penche le galet. Il ne le jette pas. Je le pose. Je ne le lance pas. Il descend deux marches. Le galet rejoint la paume. Le ballon attend dans l'herbe, témoin rond. La pierre est arrivée. Maintenant le mot, s'il te plaît ? Nino pose les deux pieds dans l'herbe avant de parler. Une voix trop près, aux crochets. Mon ventre s'est serré. La maîtresse a dit : tu le donnes, ce soir. Tu l'as donné. Tes pieds sont dans l'herbe. [pause]</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
@@ -9016,7 +9014,7 @@
 enfant-m|Mon ventre s'est serré.
 enfant-m|La maîtresse a dit : tu le donnes, ce soir.
 maman|Tu l'as donné.
-maman|Merci d'avoir posé tes pieds.</t>
+maman|Tes pieds sont dans l'herbe.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -9629,17 +9627,17 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Papa descend le seau, échelon par échelon, sans le balancer. Ils le portent au banc, le galet coincé au fond. Il n'a pas dévalé. Moi non plus. Nino s'assoit. Il tape l'anse, trop tôt. L'anse se tait, puis tu parles. D'accord ? Il lâche. Le plastique fait un dernier clac. En haut, le ventre, comme aux crochets. Une voix trop près. Elle m'a donné le galet. Le seau l'a gardé. Merci d'avoir laissé le clac. La phrase est entière. Le seau bleu s'adosse au banc, anse vers Nino.</t>
+          <t>Papa descend le seau, échelon par échelon, sans le balancer. Ils le portent au banc, le galet coincé au fond. Il n'a pas dévalé. Moi non plus. Nino s'assoit. Il tape l'anse, trop tôt. L'anse se tait, puis tu parles. D'accord ? Il lâche. Le plastique fait un dernier clac. En haut, le ventre, comme aux crochets. Une voix trop près. Elle m'a donné le galet. Le seau l'a gardé. Le clac est passé. La phrase est entière. Le seau bleu s'adosse au banc, anse vers Nino.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa descend le seau, échelon par échelon, sans le balancer. Ils le portent au banc, le galet coincé au fond. Il n'a pas dévalé. Moi non plus. Nino s'assoit. Il tape l'anse, trop tôt. L'anse se tait, puis tu parles. D'accord ? Il lâche. Le plastique fait un dernier clac. En haut, le ventre, comme aux crochets. Une voix trop près. Elle m'a donné le galet. Le seau l'a gardé. Merci d'avoir laissé le clac. La phrase est entière. Le seau bleu s'adosse au banc, anse vers Nino.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa descend le seau, échelon par échelon, sans le balancer. Ils le portent au banc, le galet coincé au fond. Il n'a pas dévalé. Moi non plus. Nino s'assoit. Il tape l'anse, trop tôt. L'anse se tait, puis tu parles. D'accord ? Il lâche. Le plastique fait un dernier clac. En haut, le ventre, comme aux crochets. Une voix trop près. Elle m'a donné le galet. Le seau l'a gardé. Le clac est passé. La phrase est entière. Le seau bleu s'adosse au banc, anse vers Nino.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Papa descend le seau, échelon par échelon, sans le balancer. Ils le portent au banc, le galet coincé au fond. Il n'a pas dévalé. Moi non plus. Nino s'assoit. Il tape l'anse, trop tôt. L'anse se tait, puis tu parles. D'accord ? Il lâche. Le plastique fait un dernier clac. En haut, le ventre, comme aux crochets. Une voix trop près. Elle m'a donné le galet. Le seau l'a gardé. Merci d'avoir laissé le clac. La phrase est entière. Le seau bleu s'adosse au banc, anse vers Nino. [pause]</t>
+          <t>Papa descend le seau, échelon par échelon, sans le balancer. Ils le portent au banc, le galet coincé au fond. Il n'a pas dévalé. Moi non plus. Nino s'assoit. Il tape l'anse, trop tôt. L'anse se tait, puis tu parles. D'accord ? Il lâche. Le plastique fait un dernier clac. En haut, le ventre, comme aux crochets. Une voix trop près. Elle m'a donné le galet. Le seau l'a gardé. Le clac est passé. La phrase est entière. Le seau bleu s'adosse au banc, anse vers Nino. [pause]</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -9787,7 +9785,7 @@
 enfant-m|Une voix trop près.
 enfant-m|Elle m'a donné le galet.
 enfant-m|Le seau l'a gardé.
-papa|Merci d'avoir laissé le clac.
+papa|Le clac est passé.
 papa|La phrase est entière.
 narrateur|Le seau bleu s'adosse au banc, anse vers Nino.</t>
         </is>
@@ -10387,17 +10385,17 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Papa tient le seau. Maman avance la paume au bord. Nino bascule le fond, un geste court, pas une cascade. Pour ta main. Pas pour l'herbe. Le galet atterrit. La paume se creuse. Un souffle d'air sent le métal du toboggan. Il est arrivé. Tes pieds sont où ? Nino saute du dernier barreau. Deux pieds dans l'herbe. Une voix trop près, aux crochets. Mon ventre s'est serré. Elle a dit de le mettre dans une main de la maison. Ma main est celle-là. Merci d'avoir visé la paume.</t>
+          <t>Papa tient le seau. Maman avance la paume au bord. Nino bascule le fond, un geste court, pas une cascade. Pour ta main. Pas pour l'herbe. Le galet atterrit. La paume se creuse. Un souffle d'air sent le métal du toboggan. Il est arrivé. Tes pieds sont où ? Nino saute du dernier barreau. Deux pieds dans l'herbe. Une voix trop près, aux crochets. Mon ventre s'est serré. Elle a dit de le mettre dans une main de la maison. Ma main est celle-là. Tu as visé la paume.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa tient le seau. Maman avance la paume au bord. Nino bascule le fond, un geste court, pas une cascade. Pour ta main. Pas pour l'herbe. Le galet atterrit. La paume se creuse. Un souffle d'air sent le métal du toboggan. Il est arrivé. Tes pieds sont où ? Nino saute du dernier barreau. Deux pieds dans l'herbe. Une voix trop près, aux crochets. Mon ventre s'est serré. Elle a dit de le mettre dans une main de la maison. Ma main est celle-là. Merci d'avoir visé la paume.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa tient le seau. Maman avance la paume au bord. Nino bascule le fond, un geste court, pas une cascade. Pour ta main. Pas pour l'herbe. Le galet atterrit. La paume se creuse. Un souffle d'air sent le métal du toboggan. Il est arrivé. Tes pieds sont où ? Nino saute du dernier barreau. Deux pieds dans l'herbe. Une voix trop près, aux crochets. Mon ventre s'est serré. Elle a dit de le mettre dans une main de la maison. Ma main est celle-là. Tu as visé la paume.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Papa tient le seau. Maman avance la paume au bord. Nino bascule le fond, un geste court, pas une cascade. Pour ta main. Pas pour l'herbe. Le galet atterrit. La paume se creuse. Un souffle d'air sent le métal du toboggan. Il est arrivé. Tes pieds sont où ? Nino saute du dernier barreau. Deux pieds dans l'herbe. Une voix trop près, aux crochets. Mon ventre s'est serré. Elle a dit de le mettre dans une main de la maison. Ma main est celle-là. Merci d'avoir visé la paume. [pause]</t>
+          <t>Papa tient le seau. Maman avance la paume au bord. Nino bascule le fond, un geste court, pas une cascade. Pour ta main. Pas pour l'herbe. Le galet atterrit. La paume se creuse. Un souffle d'air sent le métal du toboggan. Il est arrivé. Tes pieds sont où ? Nino saute du dernier barreau. Deux pieds dans l'herbe. Une voix trop près, aux crochets. Mon ventre s'est serré. Elle a dit de le mettre dans une main de la maison. Ma main est celle-là. Tu as visé la paume. [pause]</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
@@ -10547,7 +10545,7 @@
 enfant-m|Mon ventre s'est serré.
 enfant-m|Elle a dit de le mettre dans une main de la maison.
 maman|Ma main est celle-là.
-maman|Merci d'avoir visé la paume.</t>
+maman|Tu as visé la paume.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
@@ -11537,17 +11535,17 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Dans l'herbe, Nino glisse le galet, puis un bout de doudou. La poche déborde. Une oreille reste dehors. Ils se tiennent. Je peux dire. Un vélo sonne sur la piste. Il parle quand même. On laisse la sonnette. Après, toi. La sonnette file. Nino reprend, main sur l'oreille. Une voix trop près, aux crochets. Ça serrait en haut. Elle m'a donné le galet. Il voyage avec le doudou. Merci d'avoir laissé la sonnette. On a tout. L'échelle jette une ombre en barreaux sur ses chaussures.</t>
+          <t>Dans l'herbe, Nino glisse le galet, puis un bout de doudou. La poche déborde. Une oreille reste dehors. Ils se tiennent. Je peux dire. Un vélo sonne sur la piste. Il parle quand même. On laisse la sonnette. Après, toi. La sonnette file. Nino reprend, main sur l'oreille. Une voix trop près, aux crochets. Ça serrait en haut. Elle m'a donné le galet. Il voyage avec le doudou. La sonnette est partie. On a toute la phrase. L'échelle jette une ombre en barreaux sur ses chaussures.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Dans l'herbe, Nino glisse le galet, puis un bout de doudou. La poche déborde. Une oreille reste dehors. Ils se tiennent. Je peux dire. Un vélo sonne sur la piste. Il parle quand même. On laisse la &lt;emphasis level="moderate"&gt;sonnette&lt;/emphasis&gt;. Après, toi. La sonnette file. Nino reprend, main sur l'oreille. Une voix trop près, aux crochets. Ça serrait en haut. Elle m'a donné le galet. Il voyage avec le doudou. Merci d'avoir laissé la sonnette. On a tout. L'échelle jette une ombre en barreaux sur ses chaussures.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Dans l'herbe, Nino glisse le galet, puis un bout de doudou. La poche déborde. Une oreille reste dehors. Ils se tiennent. Je peux dire. Un vélo sonne sur la piste. Il parle quand même. On laisse la &lt;emphasis level="moderate"&gt;sonnette&lt;/emphasis&gt;. Après, toi. La sonnette file. Nino reprend, main sur l'oreille. Une voix trop près, aux crochets. Ça serrait en haut. Elle m'a donné le galet. Il voyage avec le doudou. La sonnette est partie. On a toute la phrase. L'échelle jette une ombre en barreaux sur ses chaussures.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Dans l'herbe, Nino glisse le galet, puis un bout de doudou. La poche déborde. Une oreille reste dehors. Ils se tiennent. Je peux dire. Un vélo sonne sur la piste. Il parle quand même. On laisse la &lt;emphasis&gt;sonnette&lt;/emphasis&gt;. Après, toi. La sonnette file. Nino reprend, main sur l'oreille. Une voix trop près, aux crochets. Ça serrait en haut. Elle m'a donné le galet. Il voyage avec le doudou. Merci d'avoir laissé la sonnette. On a tout. L'échelle jette une ombre en barreaux sur ses chaussures. [pause]</t>
+          <t>Dans l'herbe, Nino glisse le galet, puis un bout de doudou. La poche déborde. Une oreille reste dehors. Ils se tiennent. Je peux dire. Un vélo sonne sur la piste. Il parle quand même. On laisse la &lt;emphasis&gt;sonnette&lt;/emphasis&gt;. Après, toi. La sonnette file. Nino reprend, main sur l'oreille. Une voix trop près, aux crochets. Ça serrait en haut. Elle m'a donné le galet. Il voyage avec le doudou. La sonnette est partie. On a toute la phrase. L'échelle jette une ombre en barreaux sur ses chaussures. [pause]</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -11696,8 +11694,8 @@
 enfant-m|Ça serrait en haut.
 enfant-m|Elle m'a donné le galet.
 enfant-m|Il voyage avec le doudou.
-maman|Merci d'avoir laissé la sonnette.
-maman|On a tout.
+maman|La sonnette est partie.
+maman|On a toute la phrase.
 narrateur|L'échelle jette une ombre en barreaux sur ses chaussures.</t>
         </is>
       </c>
@@ -11917,17 +11915,17 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Nino garde le doudou. Il pose le galet dans la paume de maman. Le tissu reste sous son nez, une odeur de lessive et de fer. Lui a entendu là-haut. Toi, tu reçois la pierre. Maman ferme les doigts. Papa plie le filet. Le filet est plié. Tes mots peuvent sortir. Nino attendait ce pli. Il lâche le menton du doudou. Aux crochets, une voix trop près. Mon ventre s'est serré. La maîtresse a dit de le poser dans une main, ce soir. C'est fait. Merci d'avoir attendu le filet. Le doudou penche vers la paume, comme pour vérifier.</t>
+          <t>Nino garde le doudou. Il pose le galet dans la paume de maman. Le tissu reste sous son nez, une odeur de lessive et de fer. Lui a entendu là-haut. Toi, tu reçois la pierre. Maman ferme les doigts. Papa plie le filet. Le filet est plié. Tes mots peuvent sortir. Nino attendait ce pli. Il lâche le menton du doudou. Aux crochets, une voix trop près. Mon ventre s'est serré. La maîtresse a dit de le poser dans une main, ce soir. C'est fait. Le filet est plié. Le doudou penche vers la paume, comme pour vérifier.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino garde le doudou. Il pose le galet dans la paume de maman. Le tissu reste sous son nez, une odeur de &lt;emphasis level="moderate"&gt;lessive&lt;/emphasis&gt; et de fer. Lui a entendu là-haut. Toi, tu reçois la pierre. Maman ferme les doigts. Papa plie le filet. Le filet est plié. Tes mots peuvent sortir. Nino attendait ce pli. Il lâche le menton du doudou. Aux crochets, une voix trop près. Mon ventre s'est serré. La maîtresse a dit de le poser dans une main, ce soir. C'est fait. Merci d'avoir attendu le filet. Le doudou penche vers la paume, comme pour vérifier.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino garde le doudou. Il pose le galet dans la paume de maman. Le tissu reste sous son nez, une odeur de &lt;emphasis level="moderate"&gt;lessive&lt;/emphasis&gt; et de fer. Lui a entendu là-haut. Toi, tu reçois la pierre. Maman ferme les doigts. Papa plie le filet. Le filet est plié. Tes mots peuvent sortir. Nino attendait ce pli. Il lâche le menton du doudou. Aux crochets, une voix trop près. Mon ventre s'est serré. La maîtresse a dit de le poser dans une main, ce soir. C'est fait. Le filet est plié. Le doudou penche vers la paume, comme pour vérifier.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Nino garde le doudou. Il pose le galet dans la paume de maman. Le tissu reste sous son nez, une odeur de &lt;emphasis&gt;lessive&lt;/emphasis&gt; et de fer. Lui a entendu là-haut. Toi, tu reçois la pierre. Maman ferme les doigts. Papa plie le filet. Le filet est plié. Tes mots peuvent sortir. Nino attendait ce pli. Il lâche le menton du doudou. Aux crochets, une voix trop près. Mon ventre s'est serré. La maîtresse a dit de le poser dans une main, ce soir. C'est fait. Merci d'avoir attendu le filet. Le doudou penche vers la paume, comme pour vérifier. [pause]</t>
+          <t>Nino garde le doudou. Il pose le galet dans la paume de maman. Le tissu reste sous son nez, une odeur de &lt;emphasis&gt;lessive&lt;/emphasis&gt; et de fer. Lui a entendu là-haut. Toi, tu reçois la pierre. Maman ferme les doigts. Papa plie le filet. Le filet est plié. Tes mots peuvent sortir. Nino attendait ce pli. Il lâche le menton du doudou. Aux crochets, une voix trop près. Mon ventre s'est serré. La maîtresse a dit de le poser dans une main, ce soir. C'est fait. Le filet est plié. Le doudou penche vers la paume, comme pour vérifier. [pause]</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
@@ -12076,7 +12074,7 @@
 enfant-m|Mon ventre s'est serré.
 enfant-m|La maîtresse a dit de le poser dans une main, ce soir.
 maman|C'est fait.
-maman|Merci d'avoir attendu le filet.
+maman|Le filet est plié.
 narrateur|Le doudou penche vers la paume, comme pour vérifier.</t>
         </is>
       </c>
@@ -13452,17 +13450,17 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Nino laisse la chaîne. Il pousse le ballon jusqu'au banc. Ils s'assoient face aux balançoires, le poteau un peu loin. Le poum a fini. Le tic aussi. Le mot, maintenant. Un siège vide se balance. Nino parle trop tôt. On attend que le siège s'arrête, puis toute la phrase. Le siège ralentit, s'immobilise, un peu de travers. Aux crochets, une voix trop près. Ça m'a serré le ventre. La maîtresse m'a donné le galet. Je voulais une clochette. Le siège est sage. Merci d'avoir attendu. Le ballon cale le pied du banc. Le galet tient sur une latte.</t>
+          <t>Nino laisse la chaîne. Il pousse le ballon jusqu'au banc. Ils s'assoient face aux balançoires, le poteau un peu loin. Le poum a fini. Le tic aussi. Le mot, maintenant. Un siège vide se balance. Nino parle trop tôt. On attend que le siège s'arrête, puis toute la phrase. Le siège ralentit, s'immobilise, un peu de travers. Aux crochets, une voix trop près. Ça m'a serré le ventre. La maîtresse m'a donné le galet. Je voulais une clochette. Le siège est sage. Ta phrase peut marcher. Le ballon cale le pied du banc. Le galet tient sur une latte.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino laisse la chaîne. Il pousse le ballon jusqu'au banc. Ils s'assoient face aux balançoires, le poteau un peu loin. Le poum a fini. Le tic aussi. Le mot, maintenant. Un siège vide se balance. Nino parle trop tôt. On attend que le siège s'arrête, puis toute la phrase. Le siège ralentit, s'immobilise, un peu de travers. Aux crochets, une voix trop près. Ça m'a serré le ventre. La maîtresse m'a donné le galet. Je voulais une clochette. Le siège est sage. Merci d'avoir attendu. Le ballon cale le pied du banc. Le galet tient sur une latte.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino laisse la chaîne. Il pousse le ballon jusqu'au banc. Ils s'assoient face aux balançoires, le poteau un peu loin. Le poum a fini. Le tic aussi. Le mot, maintenant. Un siège vide se balance. Nino parle trop tôt. On attend que le siège s'arrête, puis toute la phrase. Le siège ralentit, s'immobilise, un peu de travers. Aux crochets, une voix trop près. Ça m'a serré le ventre. La maîtresse m'a donné le galet. Je voulais une clochette. Le siège est sage. Ta phrase peut marcher. Le ballon cale le pied du banc. Le galet tient sur une latte.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Nino laisse la chaîne. Il pousse le ballon jusqu'au banc. Ils s'assoient face aux balançoires, le poteau un peu loin. Le poum a fini. Le tic aussi. Le mot, maintenant. Un siège vide se balance. Nino parle trop tôt. On attend que le siège s'arrête, puis toute la phrase. Le siège ralentit, s'immobilise, un peu de travers. Aux crochets, une voix trop près. Ça m'a serré le ventre. La maîtresse m'a donné le galet. Je voulais une clochette. Le siège est sage. Merci d'avoir attendu. Le ballon cale le pied du banc. Le galet tient sur une latte. [pause]</t>
+          <t>Nino laisse la chaîne. Il pousse le ballon jusqu'au banc. Ils s'assoient face aux balançoires, le poteau un peu loin. Le poum a fini. Le tic aussi. Le mot, maintenant. Un siège vide se balance. Nino parle trop tôt. On attend que le siège s'arrête, puis toute la phrase. Le siège ralentit, s'immobilise, un peu de travers. Aux crochets, une voix trop près. Ça m'a serré le ventre. La maîtresse m'a donné le galet. Je voulais une clochette. Le siège est sage. Ta phrase peut marcher. Le ballon cale le pied du banc. Le galet tient sur une latte. [pause]</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
@@ -13611,7 +13609,7 @@
 enfant-m|La maîtresse m'a donné le galet.
 enfant-m|Je voulais une clochette.
 papa|Le siège est sage.
-papa|Merci d'avoir attendu.
+papa|Ta phrase peut marcher.
 narrateur|Le ballon cale le pied du banc.
 narrateur|Le galet tient sur une latte.</t>
         </is>
@@ -14214,17 +14212,17 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Nino prend le galet. Il le pose dans la paume de papa. Le ballon, sous le coude de maman, ne rebondit plus. Pour toi. La chaîne a trop parlé, avant. Papa pèse le gris. Il est plus chaud que le soir. On garde le ballon sage. Nino, tes mots ? Nino pose une main sur la chaîne, sans la bouger. Aux crochets, une voix trop près. Ça serrait. La maîtresse m'a donné ça. Je voulais que ça clique, ici. Ça a cliqué dans ma main. Merci d'avoir posé, pas lancé. Un maillon laisse une marque tiède sur les doigts de Nino.</t>
+          <t>Nino prend le galet. Il le pose dans la paume de papa. Le ballon, sous le coude de maman, ne rebondit plus. Pour toi. La chaîne a trop parlé, avant. Papa pèse le gris. Il est plus chaud que le soir. On garde le ballon sage. Nino, tes mots ? Nino pose une main sur la chaîne, sans la bouger. Aux crochets, une voix trop près. Ça serrait. La maîtresse m'a donné ça. Je voulais que ça clique, ici. Ça a cliqué dans ma main. Tu as posé, pas lancé. Un maillon laisse une marque tiède sur les doigts de Nino.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino prend le galet. Il le pose dans la paume de papa. Le ballon, sous le coude de maman, ne rebondit plus. Pour toi. La chaîne a trop parlé, avant. Papa pèse le gris. Il est plus chaud que le soir. On garde le ballon sage. Nino, tes mots ? Nino pose une main sur la chaîne, sans la bouger. Aux crochets, une voix trop près. Ça serrait. La maîtresse m'a donné ça. Je voulais que ça clique, ici. Ça a cliqué dans ma main. Merci d'avoir posé, pas lancé. Un maillon laisse une &lt;emphasis level="moderate"&gt;marque tiède&lt;/emphasis&gt; sur les doigts de Nino.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino prend le galet. Il le pose dans la paume de papa. Le ballon, sous le coude de maman, ne rebondit plus. Pour toi. La chaîne a trop parlé, avant. Papa pèse le gris. Il est plus chaud que le soir. On garde le ballon sage. Nino, tes mots ? Nino pose une main sur la chaîne, sans la bouger. Aux crochets, une voix trop près. Ça serrait. La maîtresse m'a donné ça. Je voulais que ça clique, ici. Ça a cliqué dans ma main. Tu as posé, pas lancé. Un maillon laisse une &lt;emphasis level="moderate"&gt;marque tiède&lt;/emphasis&gt; sur les doigts de Nino.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Nino prend le galet. Il le pose dans la paume de papa. Le ballon, sous le coude de maman, ne rebondit plus. Pour toi. La chaîne a trop parlé, avant. Papa pèse le gris. Il est plus chaud que le soir. On garde le ballon sage. Nino, tes mots ? Nino pose une main sur la chaîne, sans la bouger. Aux crochets, une voix trop près. Ça serrait. La maîtresse m'a donné ça. Je voulais que ça clique, ici. Ça a cliqué dans ma main. Merci d'avoir posé, pas lancé. Un maillon laisse une &lt;emphasis&gt;marque tiède&lt;/emphasis&gt; sur les doigts de Nino. [pause]</t>
+          <t>Nino prend le galet. Il le pose dans la paume de papa. Le ballon, sous le coude de maman, ne rebondit plus. Pour toi. La chaîne a trop parlé, avant. Papa pèse le gris. Il est plus chaud que le soir. On garde le ballon sage. Nino, tes mots ? Nino pose une main sur la chaîne, sans la bouger. Aux crochets, une voix trop près. Ça serrait. La maîtresse m'a donné ça. Je voulais que ça clique, ici. Ça a cliqué dans ma main. Tu as posé, pas lancé. Un maillon laisse une &lt;emphasis&gt;marque tiède&lt;/emphasis&gt; sur les doigts de Nino. [pause]</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
@@ -14373,7 +14371,7 @@
 enfant-m|La maîtresse m'a donné ça.
 enfant-m|Je voulais que ça clique, ici.
 papa|Ça a cliqué dans ma main.
-papa|Merci d'avoir posé, pas lancé.
+papa|Tu as posé, pas lancé.
 narrateur|Un maillon laisse une marque tiède sur les doigts de Nino.</t>
         </is>
       </c>
@@ -14987,17 +14985,17 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Nino soulève le seau, galet au fond, et gagne le banc. La chaîne, derrière, reste tendue, sans tic. Le seau a attrapé. Le banc va écouter. Il pose trop près du bord. L'anse bascule. Plus au milieu. Après, tes mots. Nino recale. Le bleu s'immobilise entre eux. Une voix trop près, aux crochets. Mon ventre s'est serré. Elle m'a donné le galet. Le seau l'a rattrapé sous le siège. Merci d'avoir recalé. Nous t'écoutions. Une latte du banc a une tache ronde, l'ombre du seau.</t>
+          <t>Nino soulève le seau, galet au fond, et gagne le banc. La chaîne, derrière, reste tendue, sans tic. Le seau a attrapé. Le banc va écouter. Il pose trop près du bord. L'anse bascule. Plus au milieu. Après, tes mots. Nino recale. Le bleu s'immobilise entre eux. Une voix trop près, aux crochets. Mon ventre s'est serré. Elle m'a donné le galet. Le seau l'a rattrapé sous le siège. Le seau est recalé. Nous t'écoutions. Une latte du banc a une tache ronde, l'ombre du seau.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino soulève le seau, galet au fond, et gagne le banc. La chaîne, derrière, reste tendue, sans tic. Le seau a attrapé. Le banc va écouter. Il pose trop près du bord. L'anse bascule. Plus au milieu. Après, tes mots. Nino recale. Le bleu s'immobilise entre eux. Une voix trop près, aux crochets. Mon ventre s'est serré. Elle m'a donné le galet. Le seau l'a rattrapé sous le siège. Merci d'avoir recalé. Nous t'écoutions. Une latte du banc a une &lt;emphasis level="moderate"&gt;tache ronde&lt;/emphasis&gt;, l'ombre du seau.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino soulève le seau, galet au fond, et gagne le banc. La chaîne, derrière, reste tendue, sans tic. Le seau a attrapé. Le banc va écouter. Il pose trop près du bord. L'anse bascule. Plus au milieu. Après, tes mots. Nino recale. Le bleu s'immobilise entre eux. Une voix trop près, aux crochets. Mon ventre s'est serré. Elle m'a donné le galet. Le seau l'a rattrapé sous le siège. Le seau est recalé. Nous t'écoutions. Une latte du banc a une &lt;emphasis level="moderate"&gt;tache ronde&lt;/emphasis&gt;, l'ombre du seau.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Nino soulève le seau, galet au fond, et gagne le banc. La chaîne, derrière, reste tendue, sans tic. Le seau a attrapé. Le banc va écouter. Il pose trop près du bord. L'anse bascule. Plus au milieu. Après, tes mots. Nino recale. Le bleu s'immobilise entre eux. Une voix trop près, aux crochets. Mon ventre s'est serré. Elle m'a donné le galet. Le seau l'a rattrapé sous le siège. Merci d'avoir recalé. Nous t'écoutions. Une latte du banc a une &lt;emphasis&gt;tache ronde&lt;/emphasis&gt;, l'ombre du seau. [pause]</t>
+          <t>Nino soulève le seau, galet au fond, et gagne le banc. La chaîne, derrière, reste tendue, sans tic. Le seau a attrapé. Le banc va écouter. Il pose trop près du bord. L'anse bascule. Plus au milieu. Après, tes mots. Nino recale. Le bleu s'immobilise entre eux. Une voix trop près, aux crochets. Mon ventre s'est serré. Elle m'a donné le galet. Le seau l'a rattrapé sous le siège. Le seau est recalé. Nous t'écoutions. Une latte du banc a une &lt;emphasis&gt;tache ronde&lt;/emphasis&gt;, l'ombre du seau. [pause]</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
@@ -15145,7 +15143,7 @@
 enfant-m|Mon ventre s'est serré.
 enfant-m|Elle m'a donné le galet.
 enfant-m|Le seau l'a rattrapé sous le siège.
-maman|Merci d'avoir recalé.
+maman|Le seau est recalé.
 maman|Nous t'écoutions.
 narrateur|Une latte du banc a une tache ronde, l'ombre du seau.</t>
         </is>
@@ -15749,17 +15747,17 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Nino tend le seau. Papa y plonge la paume, pas les deux. Le galet se pose, un choc sourd, contre la peau. Il est sorti du bleu. Le mot aussi. La chaîne bouge d'un souffle. Nino parle trop tôt. Deux doigts sur le maillon. Puis ta phrase. Nino tient le maillon. Le souffle passe. Une voix trop près, aux crochets. Mon ventre s'est serré. Elle m'a donné ça. Je le mets dans une main, pas par terre. Ma main l'a. Merci d'avoir tenu la chaîne. Le seau vide reste entre ses genoux, léger comme un secret fini.</t>
+          <t>Nino tend le seau. Papa y plonge la paume, pas les deux. Le galet se pose, un choc sourd, contre la peau. Il est sorti du bleu. Le mot aussi. La chaîne bouge d'un souffle. Nino parle trop tôt. Deux doigts sur le maillon. Puis ta phrase. Nino tient le maillon. Le souffle passe. Une voix trop près, aux crochets. Mon ventre s'est serré. Elle m'a donné ça. Je le mets dans une main, pas par terre. Ma main l'a. Tu as tenu la chaîne. Le seau vide reste entre ses genoux, léger comme un secret fini.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino tend le seau. Papa y plonge la paume, pas les deux. Le galet se pose, un &lt;emphasis level="moderate"&gt;choc sourd&lt;/emphasis&gt;, contre la peau. Il est sorti du bleu. Le mot aussi. La chaîne bouge d'un souffle. Nino parle trop tôt. Deux doigts sur le maillon. Puis ta phrase. Nino tient le maillon. Le souffle passe. Une voix trop près, aux crochets. Mon ventre s'est serré. Elle m'a donné ça. Je le mets dans une main, pas par terre. Ma main l'a. Merci d'avoir tenu la chaîne. Le seau vide reste entre ses genoux, léger comme un secret fini.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino tend le seau. Papa y plonge la paume, pas les deux. Le galet se pose, un &lt;emphasis level="moderate"&gt;choc sourd&lt;/emphasis&gt;, contre la peau. Il est sorti du bleu. Le mot aussi. La chaîne bouge d'un souffle. Nino parle trop tôt. Deux doigts sur le maillon. Puis ta phrase. Nino tient le maillon. Le souffle passe. Une voix trop près, aux crochets. Mon ventre s'est serré. Elle m'a donné ça. Je le mets dans une main, pas par terre. Ma main l'a. Tu as tenu la chaîne. Le seau vide reste entre ses genoux, léger comme un secret fini.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Nino tend le seau. Papa y plonge la paume, pas les deux. Le galet se pose, un &lt;emphasis&gt;choc sourd&lt;/emphasis&gt;, contre la peau. Il est sorti du bleu. Le mot aussi. La chaîne bouge d'un souffle. Nino parle trop tôt. Deux doigts sur le maillon. Puis ta phrase. Nino tient le maillon. Le souffle passe. Une voix trop près, aux crochets. Mon ventre s'est serré. Elle m'a donné ça. Je le mets dans une main, pas par terre. Ma main l'a. Merci d'avoir tenu la chaîne. Le seau vide reste entre ses genoux, léger comme un secret fini. [pause]</t>
+          <t>Nino tend le seau. Papa y plonge la paume, pas les deux. Le galet se pose, un &lt;emphasis&gt;choc sourd&lt;/emphasis&gt;, contre la peau. Il est sorti du bleu. Le mot aussi. La chaîne bouge d'un souffle. Nino parle trop tôt. Deux doigts sur le maillon. Puis ta phrase. Nino tient le maillon. Le souffle passe. Une voix trop près, aux crochets. Mon ventre s'est serré. Elle m'a donné ça. Je le mets dans une main, pas par terre. Ma main l'a. Tu as tenu la chaîne. Le seau vide reste entre ses genoux, léger comme un secret fini. [pause]</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -15909,7 +15907,7 @@
 enfant-m|Elle m'a donné ça.
 enfant-m|Je le mets dans une main, pas par terre.
 papa|Ma main l'a.
-papa|Merci d'avoir tenu la chaîne.
+papa|Tu as tenu la chaîne.
 narrateur|Le seau vide reste entre ses genoux, léger comme un secret fini.</t>
         </is>
       </c>
@@ -16519,17 +16517,17 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Nino descend le doudou du siège, galet contre le ventre du tissu. Ils gagnent le banc. La chaîne, seule, fait un arc minuscule. Toi tu n'es plus capitaine. Eux, ils écoutent. Le doudou roule. Nino le rattrape et parle ensemble. L'ami d'abord, assis. Après, toi. Nino cale le doudou entre eux. Il reprend. Aux crochets, une voix trop près. Ça m'a serré. La maîtresse m'a donné le galet. Je le disais au tissu, pas à vous. Maintenant c'est à nous. Merci d'avoir calé l'ami. Une oreille du doudou touche le galet, comme une joue.</t>
+          <t>Nino descend le doudou du siège, galet contre le ventre du tissu. Ils gagnent le banc. La chaîne, seule, fait un arc minuscule. Toi tu n'es plus capitaine. Eux, ils écoutent. Le doudou roule. Nino le rattrape et parle ensemble. L'ami d'abord, assis. Après, toi. Nino cale le doudou entre eux. Il reprend. Aux crochets, une voix trop près. Ça m'a serré. La maîtresse m'a donné le galet. Je le disais au tissu, pas à vous. Maintenant c'est à nous. L'ami est calé. Une oreille du doudou touche le galet, comme une joue.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino descend le doudou du siège, galet contre le ventre du tissu. Ils gagnent le banc. La chaîne, seule, fait un arc minuscule. Toi tu n'es plus &lt;emphasis level="moderate"&gt;capitaine&lt;/emphasis&gt;. Eux, ils écoutent. Le doudou roule. Nino le rattrape et parle ensemble. L'ami d'abord, assis. Après, toi. Nino cale le doudou entre eux. Il reprend. Aux crochets, une voix trop près. Ça m'a serré. La maîtresse m'a donné le galet. Je le disais au tissu, pas à vous. Maintenant c'est à nous. Merci d'avoir calé l'ami. Une oreille du doudou touche le galet, comme une joue.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino descend le doudou du siège, galet contre le ventre du tissu. Ils gagnent le banc. La chaîne, seule, fait un arc minuscule. Toi tu n'es plus &lt;emphasis level="moderate"&gt;capitaine&lt;/emphasis&gt;. Eux, ils écoutent. Le doudou roule. Nino le rattrape et parle ensemble. L'ami d'abord, assis. Après, toi. Nino cale le doudou entre eux. Il reprend. Aux crochets, une voix trop près. Ça m'a serré. La maîtresse m'a donné le galet. Je le disais au tissu, pas à vous. Maintenant c'est à nous. L'ami est calé. Une oreille du doudou touche le galet, comme une joue.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Nino descend le doudou du siège, galet contre le ventre du tissu. Ils gagnent le banc. La chaîne, seule, fait un arc minuscule. Toi tu n'es plus &lt;emphasis&gt;capitaine&lt;/emphasis&gt;. Eux, ils écoutent. Le doudou roule. Nino le rattrape et parle ensemble. L'ami d'abord, assis. Après, toi. Nino cale le doudou entre eux. Il reprend. Aux crochets, une voix trop près. Ça m'a serré. La maîtresse m'a donné le galet. Je le disais au tissu, pas à vous. Maintenant c'est à nous. Merci d'avoir calé l'ami. Une oreille du doudou touche le galet, comme une joue. [pause]</t>
+          <t>Nino descend le doudou du siège, galet contre le ventre du tissu. Ils gagnent le banc. La chaîne, seule, fait un arc minuscule. Toi tu n'es plus &lt;emphasis&gt;capitaine&lt;/emphasis&gt;. Eux, ils écoutent. Le doudou roule. Nino le rattrape et parle ensemble. L'ami d'abord, assis. Après, toi. Nino cale le doudou entre eux. Il reprend. Aux crochets, une voix trop près. Ça m'a serré. La maîtresse m'a donné le galet. Je le disais au tissu, pas à vous. Maintenant c'est à nous. L'ami est calé. Une oreille du doudou touche le galet, comme une joue. [pause]</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
@@ -16679,7 +16677,7 @@
 enfant-m|La maîtresse m'a donné le galet.
 enfant-m|Je le disais au tissu, pas à vous.
 maman|Maintenant c'est à nous.
-maman|Merci d'avoir calé l'ami.
+maman|L'ami est calé.
 narrateur|Une oreille du doudou touche le galet, comme une joue.</t>
         </is>
       </c>
@@ -17279,17 +17277,17 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Le doudou reste sur le siège, témoin. Nino avance vers maman. Il pose le galet dans sa paume. La chaîne, à côté, ne tic plus. Lui regarde. Toi tu reçois. Moi je dis. Maman hoche. Papa tient le siège pour qu'il ne parte pas. Le siège est tenu. Tes mots peuvent marcher. Nino pose les deux mains derrière le dos, pour ne plus couper. Aux crochets, une voix trop près. Ça m'a serré le ventre. La maîtresse m'a donné le galet. Je le mets dans ta main. Il y est. Merci d'avoir laissé tes mains derrière. Le doudou, sur le siège, penche une oreille vers la paume.</t>
+          <t>Le doudou reste sur le siège, témoin. Nino avance vers maman. Il pose le galet dans sa paume. La chaîne, à côté, ne tic plus. Lui regarde. Toi tu reçois. Moi je dis. Maman hoche. Papa tient le siège pour qu'il ne parte pas. Le siège est tenu. Tes mots peuvent marcher. Nino pose les deux mains derrière le dos, pour ne plus couper. Aux crochets, une voix trop près. Ça m'a serré le ventre. La maîtresse m'a donné le galet. Je le mets dans ta main. Il y est. Tes mains sont restées derrière. Le doudou, sur le siège, penche une oreille vers la paume.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le doudou reste sur le siège, témoin. Nino avance vers maman. Il pose le galet dans sa paume. La chaîne, à côté, ne tic plus. Lui regarde. Toi tu reçois. Moi je dis. Maman hoche. Papa tient le siège pour qu'il ne parte pas. Le siège est tenu. Tes mots peuvent marcher. Nino pose les deux &lt;emphasis level="moderate"&gt;mains derrière&lt;/emphasis&gt; le dos, pour ne plus couper. Aux crochets, une voix trop près. Ça m'a serré le ventre. La maîtresse m'a donné le galet. Je le mets dans ta main. Il y est. Merci d'avoir laissé tes mains derrière. Le doudou, sur le siège, penche une oreille vers la paume.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le doudou reste sur le siège, témoin. Nino avance vers maman. Il pose le galet dans sa paume. La chaîne, à côté, ne tic plus. Lui regarde. Toi tu reçois. Moi je dis. Maman hoche. Papa tient le siège pour qu'il ne parte pas. Le siège est tenu. Tes mots peuvent marcher. Nino pose les deux &lt;emphasis level="moderate"&gt;mains derrière&lt;/emphasis&gt; le dos, pour ne plus couper. Aux crochets, une voix trop près. Ça m'a serré le ventre. La maîtresse m'a donné le galet. Je le mets dans ta main. Il y est. Tes mains sont restées derrière. Le doudou, sur le siège, penche une oreille vers la paume.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Le doudou reste sur le siège, témoin. Nino avance vers maman. Il pose le galet dans sa paume. La chaîne, à côté, ne tic plus. Lui regarde. Toi tu reçois. Moi je dis. Maman hoche. Papa tient le siège pour qu'il ne parte pas. Le siège est tenu. Tes mots peuvent marcher. Nino pose les deux &lt;emphasis&gt;mains derrière&lt;/emphasis&gt; le dos, pour ne plus couper. Aux crochets, une voix trop près. Ça m'a serré le ventre. La maîtresse m'a donné le galet. Je le mets dans ta main. Il y est. Merci d'avoir laissé tes mains derrière. Le doudou, sur le siège, penche une oreille vers la paume. [pause]</t>
+          <t>Le doudou reste sur le siège, témoin. Nino avance vers maman. Il pose le galet dans sa paume. La chaîne, à côté, ne tic plus. Lui regarde. Toi tu reçois. Moi je dis. Maman hoche. Papa tient le siège pour qu'il ne parte pas. Le siège est tenu. Tes mots peuvent marcher. Nino pose les deux &lt;emphasis&gt;mains derrière&lt;/emphasis&gt; le dos, pour ne plus couper. Aux crochets, une voix trop près. Ça m'a serré le ventre. La maîtresse m'a donné le galet. Je le mets dans ta main. Il y est. Tes mains sont restées derrière. Le doudou, sur le siège, penche une oreille vers la paume. [pause]</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
@@ -17440,7 +17438,7 @@
 enfant-m|La maîtresse m'a donné le galet.
 enfant-m|Je le mets dans ta main.
 maman|Il y est.
-maman|Merci d'avoir laissé tes mains derrière.
+maman|Tes mains sont restées derrière.
 narrateur|Le doudou, sur le siège, penche une oreille vers la paume.</t>
         </is>
       </c>
@@ -17656,7 +17654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17769,6 +17767,13 @@
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
